--- a/LISTA_CLIENTI.xlsx
+++ b/LISTA_CLIENTI.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3782" uniqueCount="807">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3789" uniqueCount="810">
   <si>
     <t>denumire</t>
   </si>
@@ -2435,6 +2435,15 @@
   </si>
   <si>
     <t>EMINENT EXPERT TOUR SRL</t>
+  </si>
+  <si>
+    <t>ABD AUTO SHOP SRL</t>
+  </si>
+  <si>
+    <t>Str.Dragan Muntean 14</t>
+  </si>
+  <si>
+    <t>J2026018147005</t>
   </si>
 </sst>
 </file>
@@ -2469,8 +2478,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyBorder="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2481,8 +2493,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:T199" totalsRowShown="0">
-  <autoFilter ref="A1:T199"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:T200" totalsRowShown="0">
+  <autoFilter ref="A1:T200"/>
   <tableColumns count="20">
     <tableColumn id="1" name="denumire"/>
     <tableColumn id="2" name="cod_fiscal"/>
@@ -2794,7 +2806,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:T199"/>
+  <dimension ref="A1:T200"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="45.85546875" customWidth="1"/>
@@ -3056,10 +3068,10 @@
     </row>
     <row r="5" spans="1:20">
       <c r="A5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B5" t="s">
-        <v>41</v>
+        <v>807</v>
+      </c>
+      <c r="B5" s="1">
+        <v>54286204</v>
       </c>
       <c r="C5" t="s">
         <v>20</v>
@@ -3068,49 +3080,13 @@
         <v>42</v>
       </c>
       <c r="E5" t="s">
-        <v>43</v>
+        <v>84</v>
       </c>
       <c r="F5" t="s">
-        <v>44</v>
-      </c>
-      <c r="G5" t="s">
-        <v>23</v>
-      </c>
-      <c r="H5" t="s">
-        <v>23</v>
-      </c>
-      <c r="I5" t="s">
-        <v>23</v>
-      </c>
-      <c r="J5" t="s">
-        <v>23</v>
-      </c>
-      <c r="K5" t="s">
-        <v>23</v>
+        <v>808</v>
       </c>
       <c r="L5" t="s">
-        <v>45</v>
-      </c>
-      <c r="M5" t="s">
-        <v>23</v>
-      </c>
-      <c r="N5" t="s">
-        <v>23</v>
-      </c>
-      <c r="O5" t="s">
-        <v>23</v>
-      </c>
-      <c r="P5" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q5" t="s">
-        <v>23</v>
-      </c>
-      <c r="R5" t="s">
-        <v>46</v>
-      </c>
-      <c r="S5">
-        <v>0</v>
+        <v>809</v>
       </c>
       <c r="T5" t="s">
         <v>47</v>
@@ -3118,22 +3094,22 @@
     </row>
     <row r="6" spans="1:20">
       <c r="A6" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="B6" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="C6" t="s">
         <v>20</v>
       </c>
       <c r="D6" t="s">
-        <v>21</v>
+        <v>42</v>
       </c>
       <c r="E6" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="F6" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="G6" t="s">
         <v>23</v>
@@ -3151,7 +3127,7 @@
         <v>23</v>
       </c>
       <c r="L6" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="M6" t="s">
         <v>23</v>
@@ -3169,33 +3145,33 @@
         <v>23</v>
       </c>
       <c r="R6" t="s">
-        <v>29</v>
+        <v>46</v>
       </c>
       <c r="S6">
         <v>0</v>
       </c>
       <c r="T6" t="s">
-        <v>30</v>
+        <v>47</v>
       </c>
     </row>
     <row r="7" spans="1:20">
       <c r="A7" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="B7" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="C7" t="s">
         <v>20</v>
       </c>
       <c r="D7" t="s">
-        <v>42</v>
+        <v>21</v>
       </c>
       <c r="E7" t="s">
-        <v>54</v>
+        <v>38</v>
       </c>
       <c r="F7" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="G7" t="s">
         <v>23</v>
@@ -3213,7 +3189,7 @@
         <v>23</v>
       </c>
       <c r="L7" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="M7" t="s">
         <v>23</v>
@@ -3231,33 +3207,33 @@
         <v>23</v>
       </c>
       <c r="R7" t="s">
-        <v>46</v>
+        <v>29</v>
       </c>
       <c r="S7">
         <v>0</v>
       </c>
       <c r="T7" t="s">
-        <v>47</v>
+        <v>30</v>
       </c>
     </row>
     <row r="8" spans="1:20">
       <c r="A8" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="B8" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="C8" t="s">
         <v>20</v>
       </c>
       <c r="D8" t="s">
-        <v>59</v>
+        <v>42</v>
       </c>
       <c r="E8" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="F8" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="G8" t="s">
         <v>23</v>
@@ -3275,7 +3251,7 @@
         <v>23</v>
       </c>
       <c r="L8" t="s">
-        <v>23</v>
+        <v>56</v>
       </c>
       <c r="M8" t="s">
         <v>23</v>
@@ -3293,33 +3269,33 @@
         <v>23</v>
       </c>
       <c r="R8" t="s">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="S8">
         <v>0</v>
       </c>
       <c r="T8" t="s">
-        <v>23</v>
+        <v>47</v>
       </c>
     </row>
     <row r="9" spans="1:20">
       <c r="A9" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="B9" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="C9" t="s">
         <v>20</v>
       </c>
       <c r="D9" t="s">
-        <v>21</v>
+        <v>59</v>
       </c>
       <c r="E9" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="F9" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="G9" t="s">
         <v>23</v>
@@ -3337,7 +3313,7 @@
         <v>23</v>
       </c>
       <c r="L9" t="s">
-        <v>66</v>
+        <v>23</v>
       </c>
       <c r="M9" t="s">
         <v>23</v>
@@ -3355,33 +3331,33 @@
         <v>23</v>
       </c>
       <c r="R9" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="S9">
         <v>0</v>
       </c>
       <c r="T9" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
     </row>
     <row r="10" spans="1:20">
       <c r="A10" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="B10" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="C10" t="s">
         <v>20</v>
       </c>
       <c r="D10" t="s">
-        <v>42</v>
+        <v>21</v>
       </c>
       <c r="E10" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="F10" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="G10" t="s">
         <v>23</v>
@@ -3399,7 +3375,7 @@
         <v>23</v>
       </c>
       <c r="L10" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="M10" t="s">
         <v>23</v>
@@ -3417,21 +3393,21 @@
         <v>23</v>
       </c>
       <c r="R10" t="s">
-        <v>46</v>
+        <v>29</v>
       </c>
       <c r="S10">
         <v>0</v>
       </c>
       <c r="T10" t="s">
-        <v>47</v>
+        <v>30</v>
       </c>
     </row>
     <row r="11" spans="1:20">
       <c r="A11" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="B11" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="C11" t="s">
         <v>20</v>
@@ -3440,10 +3416,10 @@
         <v>42</v>
       </c>
       <c r="E11" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="F11" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="G11" t="s">
         <v>23</v>
@@ -3461,7 +3437,7 @@
         <v>23</v>
       </c>
       <c r="L11" t="s">
-        <v>23</v>
+        <v>71</v>
       </c>
       <c r="M11" t="s">
         <v>23</v>
@@ -3479,21 +3455,21 @@
         <v>23</v>
       </c>
       <c r="R11" t="s">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="S11">
         <v>0</v>
       </c>
       <c r="T11" t="s">
-        <v>23</v>
+        <v>47</v>
       </c>
     </row>
     <row r="12" spans="1:20">
       <c r="A12" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="B12" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="C12" t="s">
         <v>20</v>
@@ -3502,10 +3478,10 @@
         <v>42</v>
       </c>
       <c r="E12" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="F12" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="G12" t="s">
         <v>23</v>
@@ -3552,10 +3528,10 @@
     </row>
     <row r="13" spans="1:20">
       <c r="A13" t="s">
-        <v>805</v>
+        <v>76</v>
       </c>
       <c r="B13" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="C13" t="s">
         <v>20</v>
@@ -3564,10 +3540,10 @@
         <v>42</v>
       </c>
       <c r="E13" t="s">
-        <v>47</v>
+        <v>78</v>
       </c>
       <c r="F13" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="G13" t="s">
         <v>23</v>
@@ -3614,10 +3590,10 @@
     </row>
     <row r="14" spans="1:20">
       <c r="A14" t="s">
-        <v>82</v>
+        <v>805</v>
       </c>
       <c r="B14" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="C14" t="s">
         <v>20</v>
@@ -3626,10 +3602,10 @@
         <v>42</v>
       </c>
       <c r="E14" t="s">
-        <v>84</v>
+        <v>47</v>
       </c>
       <c r="F14" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="G14" t="s">
         <v>23</v>
@@ -3676,22 +3652,22 @@
     </row>
     <row r="15" spans="1:20">
       <c r="A15" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="B15" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="C15" t="s">
         <v>20</v>
       </c>
       <c r="D15" t="s">
-        <v>21</v>
+        <v>42</v>
       </c>
       <c r="E15" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="F15" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="G15" t="s">
         <v>23</v>
@@ -3709,7 +3685,7 @@
         <v>23</v>
       </c>
       <c r="L15" t="s">
-        <v>90</v>
+        <v>23</v>
       </c>
       <c r="M15" t="s">
         <v>23</v>
@@ -3727,33 +3703,33 @@
         <v>23</v>
       </c>
       <c r="R15" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="S15">
         <v>0</v>
       </c>
       <c r="T15" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
     </row>
     <row r="16" spans="1:20">
       <c r="A16" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="B16" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="C16" t="s">
         <v>20</v>
       </c>
       <c r="D16" t="s">
-        <v>42</v>
+        <v>21</v>
       </c>
       <c r="E16" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="F16" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="G16" t="s">
         <v>23</v>
@@ -3771,7 +3747,7 @@
         <v>23</v>
       </c>
       <c r="L16" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="M16" t="s">
         <v>23</v>
@@ -3789,21 +3765,21 @@
         <v>23</v>
       </c>
       <c r="R16" t="s">
-        <v>46</v>
+        <v>29</v>
       </c>
       <c r="S16">
         <v>0</v>
       </c>
       <c r="T16" t="s">
-        <v>47</v>
+        <v>30</v>
       </c>
     </row>
     <row r="17" spans="1:20">
       <c r="A17" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="B17" t="s">
-        <v>97</v>
+        <v>92</v>
       </c>
       <c r="C17" t="s">
         <v>20</v>
@@ -3812,10 +3788,10 @@
         <v>42</v>
       </c>
       <c r="E17" t="s">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="F17" t="s">
-        <v>99</v>
+        <v>94</v>
       </c>
       <c r="G17" t="s">
         <v>23</v>
@@ -3833,7 +3809,7 @@
         <v>23</v>
       </c>
       <c r="L17" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="M17" t="s">
         <v>23</v>
@@ -3862,22 +3838,22 @@
     </row>
     <row r="18" spans="1:20">
       <c r="A18" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="B18" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="C18" t="s">
         <v>20</v>
       </c>
       <c r="D18" t="s">
-        <v>21</v>
+        <v>42</v>
       </c>
       <c r="E18" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="F18" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="G18" t="s">
         <v>23</v>
@@ -3895,7 +3871,7 @@
         <v>23</v>
       </c>
       <c r="L18" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="M18" t="s">
         <v>23</v>
@@ -3913,21 +3889,21 @@
         <v>23</v>
       </c>
       <c r="R18" t="s">
-        <v>29</v>
+        <v>46</v>
       </c>
       <c r="S18">
         <v>0</v>
       </c>
       <c r="T18" t="s">
-        <v>30</v>
+        <v>47</v>
       </c>
     </row>
     <row r="19" spans="1:20">
       <c r="A19" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="B19" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="C19" t="s">
         <v>20</v>
@@ -3936,10 +3912,10 @@
         <v>21</v>
       </c>
       <c r="E19" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="F19" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="G19" t="s">
         <v>23</v>
@@ -3957,7 +3933,7 @@
         <v>23</v>
       </c>
       <c r="L19" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="M19" t="s">
         <v>23</v>
@@ -3986,22 +3962,22 @@
     </row>
     <row r="20" spans="1:20">
       <c r="A20" t="s">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="B20" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
       <c r="C20" t="s">
         <v>20</v>
       </c>
       <c r="D20" t="s">
-        <v>42</v>
+        <v>21</v>
       </c>
       <c r="E20" t="s">
-        <v>47</v>
+        <v>108</v>
       </c>
       <c r="F20" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="G20" t="s">
         <v>23</v>
@@ -4019,7 +3995,7 @@
         <v>23</v>
       </c>
       <c r="L20" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="M20" t="s">
         <v>23</v>
@@ -4037,33 +4013,33 @@
         <v>23</v>
       </c>
       <c r="R20" t="s">
-        <v>46</v>
+        <v>29</v>
       </c>
       <c r="S20">
         <v>0</v>
       </c>
       <c r="T20" t="s">
-        <v>47</v>
+        <v>30</v>
       </c>
     </row>
     <row r="21" spans="1:20">
       <c r="A21" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="B21" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="C21" t="s">
         <v>20</v>
       </c>
       <c r="D21" t="s">
-        <v>21</v>
+        <v>42</v>
       </c>
       <c r="E21" t="s">
-        <v>38</v>
+        <v>47</v>
       </c>
       <c r="F21" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="G21" t="s">
         <v>23</v>
@@ -4081,7 +4057,7 @@
         <v>23</v>
       </c>
       <c r="L21" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="M21" t="s">
         <v>23</v>
@@ -4099,21 +4075,21 @@
         <v>23</v>
       </c>
       <c r="R21" t="s">
-        <v>29</v>
+        <v>46</v>
       </c>
       <c r="S21">
         <v>0</v>
       </c>
       <c r="T21" t="s">
-        <v>30</v>
+        <v>47</v>
       </c>
     </row>
     <row r="22" spans="1:20">
       <c r="A22" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="B22" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="C22" t="s">
         <v>20</v>
@@ -4122,10 +4098,10 @@
         <v>21</v>
       </c>
       <c r="E22" t="s">
-        <v>64</v>
+        <v>38</v>
       </c>
       <c r="F22" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="G22" t="s">
         <v>23</v>
@@ -4143,7 +4119,7 @@
         <v>23</v>
       </c>
       <c r="L22" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="M22" t="s">
         <v>23</v>
@@ -4172,22 +4148,22 @@
     </row>
     <row r="23" spans="1:20">
       <c r="A23" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="B23" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="C23" t="s">
         <v>20</v>
       </c>
       <c r="D23" t="s">
-        <v>42</v>
+        <v>21</v>
       </c>
       <c r="E23" t="s">
-        <v>84</v>
+        <v>64</v>
       </c>
       <c r="F23" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="G23" t="s">
         <v>23</v>
@@ -4205,7 +4181,7 @@
         <v>23</v>
       </c>
       <c r="L23" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="M23" t="s">
         <v>23</v>
@@ -4223,33 +4199,33 @@
         <v>23</v>
       </c>
       <c r="R23" t="s">
-        <v>46</v>
+        <v>29</v>
       </c>
       <c r="S23">
         <v>0</v>
       </c>
       <c r="T23" t="s">
-        <v>47</v>
+        <v>30</v>
       </c>
     </row>
     <row r="24" spans="1:20">
       <c r="A24" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="B24" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="C24" t="s">
         <v>20</v>
       </c>
       <c r="D24" t="s">
-        <v>21</v>
+        <v>42</v>
       </c>
       <c r="E24" t="s">
-        <v>129</v>
+        <v>84</v>
       </c>
       <c r="F24" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="G24" t="s">
         <v>23</v>
@@ -4267,7 +4243,7 @@
         <v>23</v>
       </c>
       <c r="L24" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="M24" t="s">
         <v>23</v>
@@ -4285,21 +4261,21 @@
         <v>23</v>
       </c>
       <c r="R24" t="s">
-        <v>29</v>
+        <v>46</v>
       </c>
       <c r="S24">
         <v>0</v>
       </c>
       <c r="T24" t="s">
-        <v>30</v>
+        <v>47</v>
       </c>
     </row>
     <row r="25" spans="1:20">
       <c r="A25" t="s">
-        <v>132</v>
+        <v>127</v>
       </c>
       <c r="B25" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="C25" t="s">
         <v>20</v>
@@ -4308,10 +4284,10 @@
         <v>21</v>
       </c>
       <c r="E25" t="s">
-        <v>38</v>
+        <v>129</v>
       </c>
       <c r="F25" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="G25" t="s">
         <v>23</v>
@@ -4329,7 +4305,7 @@
         <v>23</v>
       </c>
       <c r="L25" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="M25" t="s">
         <v>23</v>
@@ -4358,10 +4334,10 @@
     </row>
     <row r="26" spans="1:20">
       <c r="A26" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="B26" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="C26" t="s">
         <v>20</v>
@@ -4370,10 +4346,10 @@
         <v>21</v>
       </c>
       <c r="E26" t="s">
-        <v>138</v>
+        <v>38</v>
       </c>
       <c r="F26" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
       <c r="G26" t="s">
         <v>23</v>
@@ -4391,7 +4367,7 @@
         <v>23</v>
       </c>
       <c r="L26" t="s">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="M26" t="s">
         <v>23</v>
@@ -4420,22 +4396,22 @@
     </row>
     <row r="27" spans="1:20">
       <c r="A27" t="s">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="B27" t="s">
-        <v>142</v>
+        <v>137</v>
       </c>
       <c r="C27" t="s">
         <v>20</v>
       </c>
       <c r="D27" t="s">
-        <v>42</v>
+        <v>21</v>
       </c>
       <c r="E27" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="F27" t="s">
-        <v>144</v>
+        <v>139</v>
       </c>
       <c r="G27" t="s">
         <v>23</v>
@@ -4453,7 +4429,7 @@
         <v>23</v>
       </c>
       <c r="L27" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="M27" t="s">
         <v>23</v>
@@ -4471,21 +4447,21 @@
         <v>23</v>
       </c>
       <c r="R27" t="s">
-        <v>46</v>
+        <v>29</v>
       </c>
       <c r="S27">
         <v>0</v>
       </c>
       <c r="T27" t="s">
-        <v>47</v>
+        <v>30</v>
       </c>
     </row>
     <row r="28" spans="1:20">
       <c r="A28" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="B28" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="C28" t="s">
         <v>20</v>
@@ -4494,10 +4470,10 @@
         <v>42</v>
       </c>
       <c r="E28" t="s">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="F28" t="s">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="G28" t="s">
         <v>23</v>
@@ -4515,7 +4491,7 @@
         <v>23</v>
       </c>
       <c r="L28" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="M28" t="s">
         <v>23</v>
@@ -4544,22 +4520,22 @@
     </row>
     <row r="29" spans="1:20">
       <c r="A29" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="B29" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="C29" t="s">
         <v>20</v>
       </c>
       <c r="D29" t="s">
-        <v>21</v>
+        <v>42</v>
       </c>
       <c r="E29" t="s">
-        <v>38</v>
+        <v>148</v>
       </c>
       <c r="F29" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="G29" t="s">
         <v>23</v>
@@ -4577,7 +4553,7 @@
         <v>23</v>
       </c>
       <c r="L29" t="s">
-        <v>23</v>
+        <v>150</v>
       </c>
       <c r="M29" t="s">
         <v>23</v>
@@ -4595,21 +4571,21 @@
         <v>23</v>
       </c>
       <c r="R29" t="s">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="S29">
         <v>0</v>
       </c>
       <c r="T29" t="s">
-        <v>23</v>
+        <v>47</v>
       </c>
     </row>
     <row r="30" spans="1:20">
       <c r="A30" t="s">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="B30" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="C30" t="s">
         <v>20</v>
@@ -4618,10 +4594,10 @@
         <v>21</v>
       </c>
       <c r="E30" t="s">
-        <v>108</v>
+        <v>38</v>
       </c>
       <c r="F30" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="G30" t="s">
         <v>23</v>
@@ -4639,7 +4615,7 @@
         <v>23</v>
       </c>
       <c r="L30" t="s">
-        <v>159</v>
+        <v>23</v>
       </c>
       <c r="M30" t="s">
         <v>23</v>
@@ -4657,33 +4633,33 @@
         <v>23</v>
       </c>
       <c r="R30" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="S30">
         <v>0</v>
       </c>
       <c r="T30" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
     </row>
     <row r="31" spans="1:20">
       <c r="A31" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="B31" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="C31" t="s">
         <v>20</v>
       </c>
       <c r="D31" t="s">
-        <v>42</v>
+        <v>21</v>
       </c>
       <c r="E31" t="s">
-        <v>148</v>
+        <v>108</v>
       </c>
       <c r="F31" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="G31" t="s">
         <v>23</v>
@@ -4701,7 +4677,7 @@
         <v>23</v>
       </c>
       <c r="L31" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="M31" t="s">
         <v>23</v>
@@ -4719,33 +4695,33 @@
         <v>23</v>
       </c>
       <c r="R31" t="s">
-        <v>46</v>
+        <v>29</v>
       </c>
       <c r="S31">
         <v>0</v>
       </c>
       <c r="T31" t="s">
-        <v>47</v>
+        <v>30</v>
       </c>
     </row>
     <row r="32" spans="1:20">
       <c r="A32" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="B32" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="C32" t="s">
         <v>20</v>
       </c>
       <c r="D32" t="s">
-        <v>166</v>
+        <v>42</v>
       </c>
       <c r="E32" t="s">
-        <v>167</v>
+        <v>148</v>
       </c>
       <c r="F32" t="s">
-        <v>168</v>
+        <v>162</v>
       </c>
       <c r="G32" t="s">
         <v>23</v>
@@ -4763,7 +4739,7 @@
         <v>23</v>
       </c>
       <c r="L32" t="s">
-        <v>23</v>
+        <v>163</v>
       </c>
       <c r="M32" t="s">
         <v>23</v>
@@ -4781,33 +4757,33 @@
         <v>23</v>
       </c>
       <c r="R32" t="s">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="S32">
         <v>0</v>
       </c>
       <c r="T32" t="s">
-        <v>23</v>
+        <v>47</v>
       </c>
     </row>
     <row r="33" spans="1:20">
       <c r="A33" t="s">
-        <v>169</v>
+        <v>164</v>
       </c>
       <c r="B33" t="s">
-        <v>170</v>
+        <v>165</v>
       </c>
       <c r="C33" t="s">
         <v>20</v>
       </c>
       <c r="D33" t="s">
-        <v>21</v>
+        <v>166</v>
       </c>
       <c r="E33" t="s">
-        <v>22</v>
+        <v>167</v>
       </c>
       <c r="F33" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="G33" t="s">
         <v>23</v>
@@ -4854,10 +4830,10 @@
     </row>
     <row r="34" spans="1:20">
       <c r="A34" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="B34" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="C34" t="s">
         <v>20</v>
@@ -4866,10 +4842,10 @@
         <v>21</v>
       </c>
       <c r="E34" t="s">
-        <v>174</v>
+        <v>22</v>
       </c>
       <c r="F34" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="G34" t="s">
         <v>23</v>
@@ -4916,10 +4892,10 @@
     </row>
     <row r="35" spans="1:20">
       <c r="A35" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="B35" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="C35" t="s">
         <v>20</v>
@@ -4928,10 +4904,10 @@
         <v>21</v>
       </c>
       <c r="E35" t="s">
-        <v>88</v>
+        <v>174</v>
       </c>
       <c r="F35" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="G35" t="s">
         <v>23</v>
@@ -4949,7 +4925,7 @@
         <v>23</v>
       </c>
       <c r="L35" t="s">
-        <v>179</v>
+        <v>23</v>
       </c>
       <c r="M35" t="s">
         <v>23</v>
@@ -4967,33 +4943,33 @@
         <v>23</v>
       </c>
       <c r="R35" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="S35">
         <v>0</v>
       </c>
       <c r="T35" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
     </row>
     <row r="36" spans="1:20">
       <c r="A36" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="B36" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="C36" t="s">
         <v>20</v>
       </c>
       <c r="D36" t="s">
-        <v>42</v>
+        <v>21</v>
       </c>
       <c r="E36" t="s">
-        <v>47</v>
+        <v>88</v>
       </c>
       <c r="F36" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="G36" t="s">
         <v>23</v>
@@ -5011,7 +4987,7 @@
         <v>23</v>
       </c>
       <c r="L36" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="M36" t="s">
         <v>23</v>
@@ -5029,21 +5005,21 @@
         <v>23</v>
       </c>
       <c r="R36" t="s">
-        <v>46</v>
+        <v>29</v>
       </c>
       <c r="S36">
         <v>0</v>
       </c>
       <c r="T36" t="s">
-        <v>47</v>
+        <v>30</v>
       </c>
     </row>
     <row r="37" spans="1:20">
       <c r="A37" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="B37" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="C37" t="s">
         <v>20</v>
@@ -5052,10 +5028,10 @@
         <v>42</v>
       </c>
       <c r="E37" t="s">
-        <v>148</v>
+        <v>47</v>
       </c>
       <c r="F37" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="G37" t="s">
         <v>23</v>
@@ -5073,7 +5049,7 @@
         <v>23</v>
       </c>
       <c r="L37" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="M37" t="s">
         <v>23</v>
@@ -5102,22 +5078,22 @@
     </row>
     <row r="38" spans="1:20">
       <c r="A38" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="B38" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="C38" t="s">
         <v>20</v>
       </c>
       <c r="D38" t="s">
-        <v>21</v>
+        <v>42</v>
       </c>
       <c r="E38" t="s">
-        <v>190</v>
+        <v>148</v>
       </c>
       <c r="F38" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="G38" t="s">
         <v>23</v>
@@ -5135,7 +5111,7 @@
         <v>23</v>
       </c>
       <c r="L38" t="s">
-        <v>23</v>
+        <v>187</v>
       </c>
       <c r="M38" t="s">
         <v>23</v>
@@ -5153,21 +5129,21 @@
         <v>23</v>
       </c>
       <c r="R38" t="s">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="S38">
         <v>0</v>
       </c>
       <c r="T38" t="s">
-        <v>23</v>
+        <v>47</v>
       </c>
     </row>
     <row r="39" spans="1:20">
       <c r="A39" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="B39" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="C39" t="s">
         <v>20</v>
@@ -5176,10 +5152,10 @@
         <v>21</v>
       </c>
       <c r="E39" t="s">
-        <v>22</v>
+        <v>190</v>
       </c>
       <c r="F39" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="G39" t="s">
         <v>23</v>
@@ -5226,10 +5202,10 @@
     </row>
     <row r="40" spans="1:20">
       <c r="A40" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="B40" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="C40" t="s">
         <v>20</v>
@@ -5238,10 +5214,10 @@
         <v>21</v>
       </c>
       <c r="E40" t="s">
-        <v>197</v>
+        <v>22</v>
       </c>
       <c r="F40" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="G40" t="s">
         <v>23</v>
@@ -5259,7 +5235,7 @@
         <v>23</v>
       </c>
       <c r="L40" t="s">
-        <v>199</v>
+        <v>23</v>
       </c>
       <c r="M40" t="s">
         <v>23</v>
@@ -5277,33 +5253,33 @@
         <v>23</v>
       </c>
       <c r="R40" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="S40">
         <v>0</v>
       </c>
       <c r="T40" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
     </row>
     <row r="41" spans="1:20">
       <c r="A41" t="s">
-        <v>200</v>
+        <v>195</v>
       </c>
       <c r="B41" t="s">
-        <v>201</v>
+        <v>196</v>
       </c>
       <c r="C41" t="s">
         <v>20</v>
       </c>
       <c r="D41" t="s">
-        <v>42</v>
+        <v>21</v>
       </c>
       <c r="E41" t="s">
-        <v>47</v>
+        <v>197</v>
       </c>
       <c r="F41" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="G41" t="s">
         <v>23</v>
@@ -5321,7 +5297,7 @@
         <v>23</v>
       </c>
       <c r="L41" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="M41" t="s">
         <v>23</v>
@@ -5339,21 +5315,21 @@
         <v>23</v>
       </c>
       <c r="R41" t="s">
-        <v>46</v>
+        <v>29</v>
       </c>
       <c r="S41">
         <v>0</v>
       </c>
       <c r="T41" t="s">
-        <v>47</v>
+        <v>30</v>
       </c>
     </row>
     <row r="42" spans="1:20">
       <c r="A42" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="B42" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="C42" t="s">
         <v>20</v>
@@ -5365,7 +5341,7 @@
         <v>47</v>
       </c>
       <c r="F42" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="G42" t="s">
         <v>23</v>
@@ -5383,7 +5359,7 @@
         <v>23</v>
       </c>
       <c r="L42" t="s">
-        <v>23</v>
+        <v>203</v>
       </c>
       <c r="M42" t="s">
         <v>23</v>
@@ -5401,33 +5377,33 @@
         <v>23</v>
       </c>
       <c r="R42" t="s">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="S42">
         <v>0</v>
       </c>
       <c r="T42" t="s">
-        <v>23</v>
+        <v>47</v>
       </c>
     </row>
     <row r="43" spans="1:20">
       <c r="A43" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="B43" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="C43" t="s">
         <v>20</v>
       </c>
       <c r="D43" t="s">
-        <v>21</v>
+        <v>42</v>
       </c>
       <c r="E43" t="s">
-        <v>209</v>
+        <v>47</v>
       </c>
       <c r="F43" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="G43" t="s">
         <v>23</v>
@@ -5445,7 +5421,7 @@
         <v>23</v>
       </c>
       <c r="L43" t="s">
-        <v>211</v>
+        <v>23</v>
       </c>
       <c r="M43" t="s">
         <v>23</v>
@@ -5463,21 +5439,21 @@
         <v>23</v>
       </c>
       <c r="R43" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="S43">
         <v>0</v>
       </c>
       <c r="T43" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
     </row>
     <row r="44" spans="1:20">
       <c r="A44" t="s">
-        <v>212</v>
+        <v>207</v>
       </c>
       <c r="B44" t="s">
-        <v>213</v>
+        <v>208</v>
       </c>
       <c r="C44" t="s">
         <v>20</v>
@@ -5486,10 +5462,10 @@
         <v>21</v>
       </c>
       <c r="E44" t="s">
-        <v>88</v>
+        <v>209</v>
       </c>
       <c r="F44" t="s">
-        <v>214</v>
+        <v>210</v>
       </c>
       <c r="G44" t="s">
         <v>23</v>
@@ -5507,7 +5483,7 @@
         <v>23</v>
       </c>
       <c r="L44" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="M44" t="s">
         <v>23</v>
@@ -5536,10 +5512,10 @@
     </row>
     <row r="45" spans="1:20">
       <c r="A45" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="B45" t="s">
-        <v>217</v>
+        <v>213</v>
       </c>
       <c r="C45" t="s">
         <v>20</v>
@@ -5548,10 +5524,10 @@
         <v>21</v>
       </c>
       <c r="E45" t="s">
-        <v>64</v>
+        <v>88</v>
       </c>
       <c r="F45" t="s">
-        <v>218</v>
+        <v>214</v>
       </c>
       <c r="G45" t="s">
         <v>23</v>
@@ -5569,7 +5545,7 @@
         <v>23</v>
       </c>
       <c r="L45" t="s">
-        <v>23</v>
+        <v>215</v>
       </c>
       <c r="M45" t="s">
         <v>23</v>
@@ -5587,21 +5563,21 @@
         <v>23</v>
       </c>
       <c r="R45" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="S45">
         <v>0</v>
       </c>
       <c r="T45" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
     </row>
     <row r="46" spans="1:20">
       <c r="A46" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="B46" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="C46" t="s">
         <v>20</v>
@@ -5610,10 +5586,10 @@
         <v>21</v>
       </c>
       <c r="E46" t="s">
-        <v>38</v>
+        <v>64</v>
       </c>
       <c r="F46" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="G46" t="s">
         <v>23</v>
@@ -5631,7 +5607,7 @@
         <v>23</v>
       </c>
       <c r="L46" t="s">
-        <v>222</v>
+        <v>23</v>
       </c>
       <c r="M46" t="s">
         <v>23</v>
@@ -5649,21 +5625,21 @@
         <v>23</v>
       </c>
       <c r="R46" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="S46">
         <v>0</v>
       </c>
       <c r="T46" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
     </row>
     <row r="47" spans="1:20">
       <c r="A47" t="s">
-        <v>223</v>
+        <v>219</v>
       </c>
       <c r="B47" t="s">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="C47" t="s">
         <v>20</v>
@@ -5672,10 +5648,10 @@
         <v>21</v>
       </c>
       <c r="E47" t="s">
-        <v>225</v>
+        <v>38</v>
       </c>
       <c r="F47" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="G47" t="s">
         <v>23</v>
@@ -5693,7 +5669,7 @@
         <v>23</v>
       </c>
       <c r="L47" t="s">
-        <v>23</v>
+        <v>222</v>
       </c>
       <c r="M47" t="s">
         <v>23</v>
@@ -5711,21 +5687,21 @@
         <v>23</v>
       </c>
       <c r="R47" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="S47">
         <v>0</v>
       </c>
       <c r="T47" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
     </row>
     <row r="48" spans="1:20">
       <c r="A48" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="B48" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="C48" t="s">
         <v>20</v>
@@ -5734,10 +5710,10 @@
         <v>21</v>
       </c>
       <c r="E48" t="s">
-        <v>38</v>
+        <v>225</v>
       </c>
       <c r="F48" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="G48" t="s">
         <v>23</v>
@@ -5755,7 +5731,7 @@
         <v>23</v>
       </c>
       <c r="L48" t="s">
-        <v>230</v>
+        <v>23</v>
       </c>
       <c r="M48" t="s">
         <v>23</v>
@@ -5773,33 +5749,33 @@
         <v>23</v>
       </c>
       <c r="R48" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="S48">
         <v>0</v>
       </c>
       <c r="T48" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
     </row>
     <row r="49" spans="1:20">
       <c r="A49" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="B49" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="C49" t="s">
         <v>20</v>
       </c>
       <c r="D49" t="s">
-        <v>42</v>
+        <v>21</v>
       </c>
       <c r="E49" t="s">
-        <v>148</v>
+        <v>38</v>
       </c>
       <c r="F49" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="G49" t="s">
         <v>23</v>
@@ -5817,7 +5793,7 @@
         <v>23</v>
       </c>
       <c r="L49" t="s">
-        <v>23</v>
+        <v>230</v>
       </c>
       <c r="M49" t="s">
         <v>23</v>
@@ -5835,21 +5811,21 @@
         <v>23</v>
       </c>
       <c r="R49" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="S49">
         <v>0</v>
       </c>
       <c r="T49" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
     </row>
     <row r="50" spans="1:20">
       <c r="A50" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="B50" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="C50" t="s">
         <v>20</v>
@@ -5858,10 +5834,10 @@
         <v>42</v>
       </c>
       <c r="E50" t="s">
-        <v>47</v>
+        <v>148</v>
       </c>
       <c r="F50" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="G50" t="s">
         <v>23</v>
@@ -5879,7 +5855,7 @@
         <v>23</v>
       </c>
       <c r="L50" t="s">
-        <v>237</v>
+        <v>23</v>
       </c>
       <c r="M50" t="s">
         <v>23</v>
@@ -5897,33 +5873,33 @@
         <v>23</v>
       </c>
       <c r="R50" t="s">
-        <v>46</v>
+        <v>23</v>
       </c>
       <c r="S50">
         <v>0</v>
       </c>
       <c r="T50" t="s">
-        <v>47</v>
+        <v>23</v>
       </c>
     </row>
     <row r="51" spans="1:20">
       <c r="A51" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
       <c r="B51" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="C51" t="s">
         <v>20</v>
       </c>
       <c r="D51" t="s">
-        <v>21</v>
+        <v>42</v>
       </c>
       <c r="E51" t="s">
-        <v>22</v>
+        <v>47</v>
       </c>
       <c r="F51" t="s">
-        <v>240</v>
+        <v>236</v>
       </c>
       <c r="G51" t="s">
         <v>23</v>
@@ -5941,7 +5917,7 @@
         <v>23</v>
       </c>
       <c r="L51" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
       <c r="M51" t="s">
         <v>23</v>
@@ -5959,21 +5935,21 @@
         <v>23</v>
       </c>
       <c r="R51" t="s">
-        <v>29</v>
+        <v>46</v>
       </c>
       <c r="S51">
         <v>0</v>
       </c>
       <c r="T51" t="s">
-        <v>30</v>
+        <v>47</v>
       </c>
     </row>
     <row r="52" spans="1:20">
       <c r="A52" t="s">
-        <v>242</v>
+        <v>238</v>
       </c>
       <c r="B52" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="C52" t="s">
         <v>20</v>
@@ -5982,10 +5958,10 @@
         <v>21</v>
       </c>
       <c r="E52" t="s">
-        <v>244</v>
+        <v>22</v>
       </c>
       <c r="F52" t="s">
-        <v>245</v>
+        <v>240</v>
       </c>
       <c r="G52" t="s">
         <v>23</v>
@@ -6003,7 +5979,7 @@
         <v>23</v>
       </c>
       <c r="L52" t="s">
-        <v>23</v>
+        <v>241</v>
       </c>
       <c r="M52" t="s">
         <v>23</v>
@@ -6021,33 +5997,33 @@
         <v>23</v>
       </c>
       <c r="R52" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="S52">
         <v>0</v>
       </c>
       <c r="T52" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
     </row>
     <row r="53" spans="1:20">
       <c r="A53" t="s">
-        <v>806</v>
+        <v>242</v>
       </c>
       <c r="B53" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="C53" t="s">
         <v>20</v>
       </c>
       <c r="D53" t="s">
-        <v>42</v>
+        <v>21</v>
       </c>
       <c r="E53" t="s">
-        <v>69</v>
+        <v>244</v>
       </c>
       <c r="F53" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="G53" t="s">
         <v>23</v>
@@ -6094,22 +6070,22 @@
     </row>
     <row r="54" spans="1:20">
       <c r="A54" t="s">
-        <v>248</v>
+        <v>806</v>
       </c>
       <c r="B54" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="C54" t="s">
         <v>20</v>
       </c>
       <c r="D54" t="s">
-        <v>21</v>
+        <v>42</v>
       </c>
       <c r="E54" t="s">
-        <v>250</v>
+        <v>69</v>
       </c>
       <c r="F54" t="s">
-        <v>251</v>
+        <v>247</v>
       </c>
       <c r="G54" t="s">
         <v>23</v>
@@ -6145,33 +6121,33 @@
         <v>23</v>
       </c>
       <c r="R54" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="S54">
         <v>0</v>
       </c>
       <c r="T54" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
     </row>
     <row r="55" spans="1:20">
       <c r="A55" t="s">
-        <v>252</v>
+        <v>248</v>
       </c>
       <c r="B55" t="s">
-        <v>253</v>
+        <v>249</v>
       </c>
       <c r="C55" t="s">
         <v>20</v>
       </c>
       <c r="D55" t="s">
-        <v>42</v>
+        <v>21</v>
       </c>
       <c r="E55" t="s">
-        <v>47</v>
+        <v>250</v>
       </c>
       <c r="F55" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="G55" t="s">
         <v>23</v>
@@ -6207,21 +6183,21 @@
         <v>23</v>
       </c>
       <c r="R55" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="S55">
         <v>0</v>
       </c>
       <c r="T55" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
     </row>
     <row r="56" spans="1:20">
       <c r="A56" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="B56" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="C56" t="s">
         <v>20</v>
@@ -6230,10 +6206,10 @@
         <v>42</v>
       </c>
       <c r="E56" t="s">
-        <v>84</v>
+        <v>47</v>
       </c>
       <c r="F56" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="G56" t="s">
         <v>23</v>
@@ -6251,7 +6227,7 @@
         <v>23</v>
       </c>
       <c r="L56" t="s">
-        <v>258</v>
+        <v>23</v>
       </c>
       <c r="M56" t="s">
         <v>23</v>
@@ -6269,33 +6245,33 @@
         <v>23</v>
       </c>
       <c r="R56" t="s">
-        <v>46</v>
+        <v>23</v>
       </c>
       <c r="S56">
         <v>0</v>
       </c>
       <c r="T56" t="s">
-        <v>47</v>
+        <v>23</v>
       </c>
     </row>
     <row r="57" spans="1:20">
       <c r="A57" t="s">
-        <v>259</v>
+        <v>255</v>
       </c>
       <c r="B57" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="C57" t="s">
         <v>20</v>
       </c>
       <c r="D57" t="s">
-        <v>154</v>
+        <v>42</v>
       </c>
       <c r="E57" t="s">
-        <v>155</v>
+        <v>84</v>
       </c>
       <c r="F57" t="s">
-        <v>261</v>
+        <v>257</v>
       </c>
       <c r="G57" t="s">
         <v>23</v>
@@ -6313,7 +6289,7 @@
         <v>23</v>
       </c>
       <c r="L57" t="s">
-        <v>23</v>
+        <v>258</v>
       </c>
       <c r="M57" t="s">
         <v>23</v>
@@ -6331,33 +6307,33 @@
         <v>23</v>
       </c>
       <c r="R57" t="s">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="S57">
         <v>0</v>
       </c>
       <c r="T57" t="s">
-        <v>23</v>
+        <v>47</v>
       </c>
     </row>
     <row r="58" spans="1:20">
       <c r="A58" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="B58" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="C58" t="s">
         <v>20</v>
       </c>
       <c r="D58" t="s">
-        <v>21</v>
+        <v>154</v>
       </c>
       <c r="E58" t="s">
-        <v>88</v>
+        <v>155</v>
       </c>
       <c r="F58" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="G58" t="s">
         <v>23</v>
@@ -6375,7 +6351,7 @@
         <v>23</v>
       </c>
       <c r="L58" t="s">
-        <v>265</v>
+        <v>23</v>
       </c>
       <c r="M58" t="s">
         <v>23</v>
@@ -6393,33 +6369,33 @@
         <v>23</v>
       </c>
       <c r="R58" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="S58">
         <v>0</v>
       </c>
       <c r="T58" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
     </row>
     <row r="59" spans="1:20">
       <c r="A59" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="B59" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="C59" t="s">
         <v>20</v>
       </c>
       <c r="D59" t="s">
-        <v>42</v>
+        <v>21</v>
       </c>
       <c r="E59" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="F59" t="s">
-        <v>268</v>
+        <v>264</v>
       </c>
       <c r="G59" t="s">
         <v>23</v>
@@ -6437,7 +6413,7 @@
         <v>23</v>
       </c>
       <c r="L59" t="s">
-        <v>269</v>
+        <v>265</v>
       </c>
       <c r="M59" t="s">
         <v>23</v>
@@ -6455,21 +6431,21 @@
         <v>23</v>
       </c>
       <c r="R59" t="s">
-        <v>46</v>
+        <v>29</v>
       </c>
       <c r="S59">
         <v>0</v>
       </c>
       <c r="T59" t="s">
-        <v>47</v>
+        <v>30</v>
       </c>
     </row>
     <row r="60" spans="1:20">
       <c r="A60" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="B60" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="C60" t="s">
         <v>20</v>
@@ -6478,10 +6454,10 @@
         <v>42</v>
       </c>
       <c r="E60" t="s">
-        <v>69</v>
+        <v>84</v>
       </c>
       <c r="F60" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
       <c r="G60" t="s">
         <v>23</v>
@@ -6499,7 +6475,7 @@
         <v>23</v>
       </c>
       <c r="L60" t="s">
-        <v>273</v>
+        <v>269</v>
       </c>
       <c r="M60" t="s">
         <v>23</v>
@@ -6528,10 +6504,10 @@
     </row>
     <row r="61" spans="1:20">
       <c r="A61" t="s">
-        <v>274</v>
+        <v>270</v>
       </c>
       <c r="B61" t="s">
-        <v>275</v>
+        <v>271</v>
       </c>
       <c r="C61" t="s">
         <v>20</v>
@@ -6540,10 +6516,10 @@
         <v>42</v>
       </c>
       <c r="E61" t="s">
-        <v>276</v>
+        <v>69</v>
       </c>
       <c r="F61" t="s">
-        <v>277</v>
+        <v>272</v>
       </c>
       <c r="G61" t="s">
         <v>23</v>
@@ -6561,7 +6537,7 @@
         <v>23</v>
       </c>
       <c r="L61" t="s">
-        <v>23</v>
+        <v>273</v>
       </c>
       <c r="M61" t="s">
         <v>23</v>
@@ -6579,21 +6555,21 @@
         <v>23</v>
       </c>
       <c r="R61" t="s">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="S61">
         <v>0</v>
       </c>
       <c r="T61" t="s">
-        <v>23</v>
+        <v>47</v>
       </c>
     </row>
     <row r="62" spans="1:20">
       <c r="A62" t="s">
-        <v>278</v>
+        <v>274</v>
       </c>
       <c r="B62" t="s">
-        <v>279</v>
+        <v>275</v>
       </c>
       <c r="C62" t="s">
         <v>20</v>
@@ -6602,10 +6578,10 @@
         <v>42</v>
       </c>
       <c r="E62" t="s">
-        <v>280</v>
+        <v>276</v>
       </c>
       <c r="F62" t="s">
-        <v>281</v>
+        <v>277</v>
       </c>
       <c r="G62" t="s">
         <v>23</v>
@@ -6623,7 +6599,7 @@
         <v>23</v>
       </c>
       <c r="L62" t="s">
-        <v>282</v>
+        <v>23</v>
       </c>
       <c r="M62" t="s">
         <v>23</v>
@@ -6641,21 +6617,21 @@
         <v>23</v>
       </c>
       <c r="R62" t="s">
-        <v>46</v>
+        <v>23</v>
       </c>
       <c r="S62">
         <v>0</v>
       </c>
       <c r="T62" t="s">
-        <v>47</v>
+        <v>23</v>
       </c>
     </row>
     <row r="63" spans="1:20">
       <c r="A63" t="s">
-        <v>283</v>
+        <v>278</v>
       </c>
       <c r="B63" t="s">
-        <v>284</v>
+        <v>279</v>
       </c>
       <c r="C63" t="s">
         <v>20</v>
@@ -6664,60 +6640,60 @@
         <v>42</v>
       </c>
       <c r="E63" t="s">
+        <v>280</v>
+      </c>
+      <c r="F63" t="s">
+        <v>281</v>
+      </c>
+      <c r="G63" t="s">
+        <v>23</v>
+      </c>
+      <c r="H63" t="s">
+        <v>23</v>
+      </c>
+      <c r="I63" t="s">
+        <v>23</v>
+      </c>
+      <c r="J63" t="s">
+        <v>23</v>
+      </c>
+      <c r="K63" t="s">
+        <v>23</v>
+      </c>
+      <c r="L63" t="s">
+        <v>282</v>
+      </c>
+      <c r="M63" t="s">
+        <v>23</v>
+      </c>
+      <c r="N63" t="s">
+        <v>23</v>
+      </c>
+      <c r="O63" t="s">
+        <v>23</v>
+      </c>
+      <c r="P63" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q63" t="s">
+        <v>23</v>
+      </c>
+      <c r="R63" t="s">
+        <v>46</v>
+      </c>
+      <c r="S63">
+        <v>0</v>
+      </c>
+      <c r="T63" t="s">
         <v>47</v>
-      </c>
-      <c r="F63" t="s">
-        <v>285</v>
-      </c>
-      <c r="G63" t="s">
-        <v>23</v>
-      </c>
-      <c r="H63" t="s">
-        <v>23</v>
-      </c>
-      <c r="I63" t="s">
-        <v>23</v>
-      </c>
-      <c r="J63" t="s">
-        <v>23</v>
-      </c>
-      <c r="K63" t="s">
-        <v>23</v>
-      </c>
-      <c r="L63" t="s">
-        <v>23</v>
-      </c>
-      <c r="M63" t="s">
-        <v>23</v>
-      </c>
-      <c r="N63" t="s">
-        <v>23</v>
-      </c>
-      <c r="O63" t="s">
-        <v>23</v>
-      </c>
-      <c r="P63" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q63" t="s">
-        <v>23</v>
-      </c>
-      <c r="R63" t="s">
-        <v>23</v>
-      </c>
-      <c r="S63">
-        <v>0</v>
-      </c>
-      <c r="T63" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="64" spans="1:20">
       <c r="A64" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="B64" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="C64" t="s">
         <v>20</v>
@@ -6726,10 +6702,10 @@
         <v>42</v>
       </c>
       <c r="E64" t="s">
-        <v>148</v>
+        <v>47</v>
       </c>
       <c r="F64" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="G64" t="s">
         <v>23</v>
@@ -6776,22 +6752,22 @@
     </row>
     <row r="65" spans="1:20">
       <c r="A65" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="B65" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="C65" t="s">
         <v>20</v>
       </c>
       <c r="D65" t="s">
-        <v>21</v>
+        <v>42</v>
       </c>
       <c r="E65" t="s">
-        <v>291</v>
+        <v>148</v>
       </c>
       <c r="F65" t="s">
-        <v>292</v>
+        <v>288</v>
       </c>
       <c r="G65" t="s">
         <v>23</v>
@@ -6838,22 +6814,22 @@
     </row>
     <row r="66" spans="1:20">
       <c r="A66" t="s">
-        <v>293</v>
+        <v>289</v>
       </c>
       <c r="B66" t="s">
-        <v>294</v>
+        <v>290</v>
       </c>
       <c r="C66" t="s">
         <v>20</v>
       </c>
       <c r="D66" t="s">
-        <v>42</v>
+        <v>21</v>
       </c>
       <c r="E66" t="s">
-        <v>84</v>
+        <v>291</v>
       </c>
       <c r="F66" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="G66" t="s">
         <v>23</v>
@@ -6871,7 +6847,7 @@
         <v>23</v>
       </c>
       <c r="L66" t="s">
-        <v>296</v>
+        <v>23</v>
       </c>
       <c r="M66" t="s">
         <v>23</v>
@@ -6889,33 +6865,33 @@
         <v>23</v>
       </c>
       <c r="R66" t="s">
-        <v>46</v>
+        <v>23</v>
       </c>
       <c r="S66">
         <v>0</v>
       </c>
       <c r="T66" t="s">
-        <v>47</v>
+        <v>23</v>
       </c>
     </row>
     <row r="67" spans="1:20">
       <c r="A67" t="s">
-        <v>297</v>
+        <v>293</v>
       </c>
       <c r="B67" t="s">
-        <v>298</v>
+        <v>294</v>
       </c>
       <c r="C67" t="s">
         <v>20</v>
       </c>
       <c r="D67" t="s">
-        <v>21</v>
+        <v>42</v>
       </c>
       <c r="E67" t="s">
-        <v>299</v>
+        <v>84</v>
       </c>
       <c r="F67" t="s">
-        <v>300</v>
+        <v>295</v>
       </c>
       <c r="G67" t="s">
         <v>23</v>
@@ -6933,7 +6909,7 @@
         <v>23</v>
       </c>
       <c r="L67" t="s">
-        <v>301</v>
+        <v>296</v>
       </c>
       <c r="M67" t="s">
         <v>23</v>
@@ -6951,21 +6927,21 @@
         <v>23</v>
       </c>
       <c r="R67" t="s">
-        <v>29</v>
+        <v>46</v>
       </c>
       <c r="S67">
         <v>0</v>
       </c>
       <c r="T67" t="s">
-        <v>30</v>
+        <v>47</v>
       </c>
     </row>
     <row r="68" spans="1:20">
       <c r="A68" t="s">
-        <v>302</v>
+        <v>297</v>
       </c>
       <c r="B68" t="s">
-        <v>303</v>
+        <v>298</v>
       </c>
       <c r="C68" t="s">
         <v>20</v>
@@ -6974,10 +6950,10 @@
         <v>21</v>
       </c>
       <c r="E68" t="s">
-        <v>22</v>
+        <v>299</v>
       </c>
       <c r="F68" t="s">
-        <v>304</v>
+        <v>300</v>
       </c>
       <c r="G68" t="s">
         <v>23</v>
@@ -6995,7 +6971,7 @@
         <v>23</v>
       </c>
       <c r="L68" t="s">
-        <v>23</v>
+        <v>301</v>
       </c>
       <c r="M68" t="s">
         <v>23</v>
@@ -7013,21 +6989,21 @@
         <v>23</v>
       </c>
       <c r="R68" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="S68">
         <v>0</v>
       </c>
       <c r="T68" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
     </row>
     <row r="69" spans="1:20">
       <c r="A69" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="B69" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="C69" t="s">
         <v>20</v>
@@ -7039,7 +7015,7 @@
         <v>22</v>
       </c>
       <c r="F69" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="G69" t="s">
         <v>23</v>
@@ -7057,7 +7033,7 @@
         <v>23</v>
       </c>
       <c r="L69" t="s">
-        <v>308</v>
+        <v>23</v>
       </c>
       <c r="M69" t="s">
         <v>23</v>
@@ -7075,33 +7051,33 @@
         <v>23</v>
       </c>
       <c r="R69" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="S69">
         <v>0</v>
       </c>
       <c r="T69" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
     </row>
     <row r="70" spans="1:20">
       <c r="A70" t="s">
-        <v>309</v>
+        <v>305</v>
       </c>
       <c r="B70" t="s">
-        <v>310</v>
+        <v>306</v>
       </c>
       <c r="C70" t="s">
         <v>20</v>
       </c>
       <c r="D70" t="s">
-        <v>42</v>
+        <v>21</v>
       </c>
       <c r="E70" t="s">
-        <v>84</v>
+        <v>22</v>
       </c>
       <c r="F70" t="s">
-        <v>311</v>
+        <v>307</v>
       </c>
       <c r="G70" t="s">
         <v>23</v>
@@ -7119,7 +7095,7 @@
         <v>23</v>
       </c>
       <c r="L70" t="s">
-        <v>23</v>
+        <v>308</v>
       </c>
       <c r="M70" t="s">
         <v>23</v>
@@ -7137,33 +7113,33 @@
         <v>23</v>
       </c>
       <c r="R70" t="s">
-        <v>46</v>
+        <v>29</v>
       </c>
       <c r="S70">
         <v>0</v>
       </c>
       <c r="T70" t="s">
-        <v>47</v>
+        <v>30</v>
       </c>
     </row>
     <row r="71" spans="1:20">
       <c r="A71" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="B71" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="C71" t="s">
         <v>20</v>
       </c>
       <c r="D71" t="s">
-        <v>21</v>
+        <v>42</v>
       </c>
       <c r="E71" t="s">
-        <v>38</v>
+        <v>84</v>
       </c>
       <c r="F71" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="G71" t="s">
         <v>23</v>
@@ -7181,7 +7157,7 @@
         <v>23</v>
       </c>
       <c r="L71" t="s">
-        <v>315</v>
+        <v>23</v>
       </c>
       <c r="M71" t="s">
         <v>23</v>
@@ -7199,21 +7175,21 @@
         <v>23</v>
       </c>
       <c r="R71" t="s">
-        <v>29</v>
+        <v>46</v>
       </c>
       <c r="S71">
         <v>0</v>
       </c>
       <c r="T71" t="s">
-        <v>30</v>
+        <v>47</v>
       </c>
     </row>
     <row r="72" spans="1:20">
       <c r="A72" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="B72" t="s">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="C72" t="s">
         <v>20</v>
@@ -7222,10 +7198,10 @@
         <v>21</v>
       </c>
       <c r="E72" t="s">
-        <v>318</v>
+        <v>38</v>
       </c>
       <c r="F72" t="s">
-        <v>319</v>
+        <v>314</v>
       </c>
       <c r="G72" t="s">
         <v>23</v>
@@ -7243,7 +7219,7 @@
         <v>23</v>
       </c>
       <c r="L72" t="s">
-        <v>320</v>
+        <v>315</v>
       </c>
       <c r="M72" t="s">
         <v>23</v>
@@ -7272,10 +7248,10 @@
     </row>
     <row r="73" spans="1:20">
       <c r="A73" t="s">
-        <v>321</v>
+        <v>316</v>
       </c>
       <c r="B73" t="s">
-        <v>322</v>
+        <v>317</v>
       </c>
       <c r="C73" t="s">
         <v>20</v>
@@ -7284,10 +7260,10 @@
         <v>21</v>
       </c>
       <c r="E73" t="s">
-        <v>38</v>
+        <v>318</v>
       </c>
       <c r="F73" t="s">
-        <v>323</v>
+        <v>319</v>
       </c>
       <c r="G73" t="s">
         <v>23</v>
@@ -7305,7 +7281,7 @@
         <v>23</v>
       </c>
       <c r="L73" t="s">
-        <v>23</v>
+        <v>320</v>
       </c>
       <c r="M73" t="s">
         <v>23</v>
@@ -7323,21 +7299,21 @@
         <v>23</v>
       </c>
       <c r="R73" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="S73">
         <v>0</v>
       </c>
       <c r="T73" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
     </row>
     <row r="74" spans="1:20">
       <c r="A74" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="B74" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="C74" t="s">
         <v>20</v>
@@ -7346,10 +7322,10 @@
         <v>21</v>
       </c>
       <c r="E74" t="s">
-        <v>108</v>
+        <v>38</v>
       </c>
       <c r="F74" t="s">
-        <v>326</v>
+        <v>323</v>
       </c>
       <c r="G74" t="s">
         <v>23</v>
@@ -7396,22 +7372,22 @@
     </row>
     <row r="75" spans="1:20">
       <c r="A75" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="B75" t="s">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="C75" t="s">
         <v>20</v>
       </c>
       <c r="D75" t="s">
-        <v>42</v>
+        <v>21</v>
       </c>
       <c r="E75" t="s">
-        <v>47</v>
+        <v>108</v>
       </c>
       <c r="F75" t="s">
-        <v>329</v>
+        <v>326</v>
       </c>
       <c r="G75" t="s">
         <v>23</v>
@@ -7429,7 +7405,7 @@
         <v>23</v>
       </c>
       <c r="L75" t="s">
-        <v>330</v>
+        <v>23</v>
       </c>
       <c r="M75" t="s">
         <v>23</v>
@@ -7447,33 +7423,33 @@
         <v>23</v>
       </c>
       <c r="R75" t="s">
-        <v>46</v>
+        <v>23</v>
       </c>
       <c r="S75">
         <v>0</v>
       </c>
       <c r="T75" t="s">
-        <v>47</v>
+        <v>23</v>
       </c>
     </row>
     <row r="76" spans="1:20">
       <c r="A76" t="s">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="B76" t="s">
-        <v>332</v>
+        <v>328</v>
       </c>
       <c r="C76" t="s">
         <v>20</v>
       </c>
       <c r="D76" t="s">
-        <v>21</v>
+        <v>42</v>
       </c>
       <c r="E76" t="s">
-        <v>333</v>
+        <v>47</v>
       </c>
       <c r="F76" t="s">
-        <v>23</v>
+        <v>329</v>
       </c>
       <c r="G76" t="s">
         <v>23</v>
@@ -7491,7 +7467,7 @@
         <v>23</v>
       </c>
       <c r="L76" t="s">
-        <v>334</v>
+        <v>330</v>
       </c>
       <c r="M76" t="s">
         <v>23</v>
@@ -7509,21 +7485,21 @@
         <v>23</v>
       </c>
       <c r="R76" t="s">
-        <v>29</v>
+        <v>46</v>
       </c>
       <c r="S76">
         <v>0</v>
       </c>
       <c r="T76" t="s">
-        <v>30</v>
+        <v>47</v>
       </c>
     </row>
     <row r="77" spans="1:20">
       <c r="A77" t="s">
-        <v>335</v>
+        <v>331</v>
       </c>
       <c r="B77" t="s">
-        <v>336</v>
+        <v>332</v>
       </c>
       <c r="C77" t="s">
         <v>20</v>
@@ -7532,10 +7508,10 @@
         <v>21</v>
       </c>
       <c r="E77" t="s">
-        <v>88</v>
+        <v>333</v>
       </c>
       <c r="F77" t="s">
-        <v>337</v>
+        <v>23</v>
       </c>
       <c r="G77" t="s">
         <v>23</v>
@@ -7553,7 +7529,7 @@
         <v>23</v>
       </c>
       <c r="L77" t="s">
-        <v>338</v>
+        <v>334</v>
       </c>
       <c r="M77" t="s">
         <v>23</v>
@@ -7582,22 +7558,22 @@
     </row>
     <row r="78" spans="1:20">
       <c r="A78" t="s">
-        <v>339</v>
+        <v>335</v>
       </c>
       <c r="B78" t="s">
-        <v>340</v>
+        <v>336</v>
       </c>
       <c r="C78" t="s">
         <v>20</v>
       </c>
       <c r="D78" t="s">
-        <v>42</v>
+        <v>21</v>
       </c>
       <c r="E78" t="s">
-        <v>143</v>
+        <v>88</v>
       </c>
       <c r="F78" t="s">
-        <v>341</v>
+        <v>337</v>
       </c>
       <c r="G78" t="s">
         <v>23</v>
@@ -7615,7 +7591,7 @@
         <v>23</v>
       </c>
       <c r="L78" t="s">
-        <v>342</v>
+        <v>338</v>
       </c>
       <c r="M78" t="s">
         <v>23</v>
@@ -7633,21 +7609,21 @@
         <v>23</v>
       </c>
       <c r="R78" t="s">
-        <v>46</v>
+        <v>29</v>
       </c>
       <c r="S78">
         <v>0</v>
       </c>
       <c r="T78" t="s">
-        <v>47</v>
+        <v>30</v>
       </c>
     </row>
     <row r="79" spans="1:20">
       <c r="A79" t="s">
-        <v>343</v>
+        <v>339</v>
       </c>
       <c r="B79" t="s">
-        <v>344</v>
+        <v>340</v>
       </c>
       <c r="C79" t="s">
         <v>20</v>
@@ -7656,10 +7632,10 @@
         <v>42</v>
       </c>
       <c r="E79" t="s">
-        <v>69</v>
+        <v>143</v>
       </c>
       <c r="F79" t="s">
-        <v>345</v>
+        <v>341</v>
       </c>
       <c r="G79" t="s">
         <v>23</v>
@@ -7677,7 +7653,7 @@
         <v>23</v>
       </c>
       <c r="L79" t="s">
-        <v>346</v>
+        <v>342</v>
       </c>
       <c r="M79" t="s">
         <v>23</v>
@@ -7706,10 +7682,10 @@
     </row>
     <row r="80" spans="1:20">
       <c r="A80" t="s">
-        <v>347</v>
+        <v>343</v>
       </c>
       <c r="B80" t="s">
-        <v>348</v>
+        <v>344</v>
       </c>
       <c r="C80" t="s">
         <v>20</v>
@@ -7718,10 +7694,10 @@
         <v>42</v>
       </c>
       <c r="E80" t="s">
-        <v>84</v>
+        <v>69</v>
       </c>
       <c r="F80" t="s">
-        <v>349</v>
+        <v>345</v>
       </c>
       <c r="G80" t="s">
         <v>23</v>
@@ -7739,7 +7715,7 @@
         <v>23</v>
       </c>
       <c r="L80" t="s">
-        <v>23</v>
+        <v>346</v>
       </c>
       <c r="M80" t="s">
         <v>23</v>
@@ -7757,21 +7733,21 @@
         <v>23</v>
       </c>
       <c r="R80" t="s">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="S80">
         <v>0</v>
       </c>
       <c r="T80" t="s">
-        <v>23</v>
+        <v>47</v>
       </c>
     </row>
     <row r="81" spans="1:20">
       <c r="A81" t="s">
-        <v>350</v>
+        <v>347</v>
       </c>
       <c r="B81" t="s">
-        <v>351</v>
+        <v>348</v>
       </c>
       <c r="C81" t="s">
         <v>20</v>
@@ -7780,10 +7756,10 @@
         <v>42</v>
       </c>
       <c r="E81" t="s">
-        <v>93</v>
+        <v>84</v>
       </c>
       <c r="F81" t="s">
-        <v>352</v>
+        <v>349</v>
       </c>
       <c r="G81" t="s">
         <v>23</v>
@@ -7801,7 +7777,7 @@
         <v>23</v>
       </c>
       <c r="L81" t="s">
-        <v>353</v>
+        <v>23</v>
       </c>
       <c r="M81" t="s">
         <v>23</v>
@@ -7819,33 +7795,33 @@
         <v>23</v>
       </c>
       <c r="R81" t="s">
-        <v>46</v>
+        <v>23</v>
       </c>
       <c r="S81">
         <v>0</v>
       </c>
       <c r="T81" t="s">
-        <v>47</v>
+        <v>23</v>
       </c>
     </row>
     <row r="82" spans="1:20">
       <c r="A82" t="s">
-        <v>354</v>
+        <v>350</v>
       </c>
       <c r="B82" t="s">
-        <v>355</v>
+        <v>351</v>
       </c>
       <c r="C82" t="s">
         <v>20</v>
       </c>
       <c r="D82" t="s">
-        <v>21</v>
+        <v>42</v>
       </c>
       <c r="E82" t="s">
-        <v>244</v>
+        <v>93</v>
       </c>
       <c r="F82" t="s">
-        <v>356</v>
+        <v>352</v>
       </c>
       <c r="G82" t="s">
         <v>23</v>
@@ -7863,7 +7839,7 @@
         <v>23</v>
       </c>
       <c r="L82" t="s">
-        <v>23</v>
+        <v>353</v>
       </c>
       <c r="M82" t="s">
         <v>23</v>
@@ -7881,21 +7857,21 @@
         <v>23</v>
       </c>
       <c r="R82" t="s">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="S82">
         <v>0</v>
       </c>
       <c r="T82" t="s">
-        <v>23</v>
+        <v>47</v>
       </c>
     </row>
     <row r="83" spans="1:20">
       <c r="A83" t="s">
-        <v>357</v>
+        <v>354</v>
       </c>
       <c r="B83" t="s">
-        <v>358</v>
+        <v>355</v>
       </c>
       <c r="C83" t="s">
         <v>20</v>
@@ -7904,10 +7880,10 @@
         <v>21</v>
       </c>
       <c r="E83" t="s">
-        <v>64</v>
+        <v>244</v>
       </c>
       <c r="F83" t="s">
-        <v>359</v>
+        <v>356</v>
       </c>
       <c r="G83" t="s">
         <v>23</v>
@@ -7925,7 +7901,7 @@
         <v>23</v>
       </c>
       <c r="L83" t="s">
-        <v>360</v>
+        <v>23</v>
       </c>
       <c r="M83" t="s">
         <v>23</v>
@@ -7943,33 +7919,33 @@
         <v>23</v>
       </c>
       <c r="R83" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="S83">
         <v>0</v>
       </c>
       <c r="T83" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
     </row>
     <row r="84" spans="1:20">
       <c r="A84" t="s">
-        <v>361</v>
+        <v>357</v>
       </c>
       <c r="B84" t="s">
-        <v>362</v>
+        <v>358</v>
       </c>
       <c r="C84" t="s">
         <v>20</v>
       </c>
       <c r="D84" t="s">
-        <v>42</v>
+        <v>21</v>
       </c>
       <c r="E84" t="s">
-        <v>84</v>
+        <v>64</v>
       </c>
       <c r="F84" t="s">
-        <v>363</v>
+        <v>359</v>
       </c>
       <c r="G84" t="s">
         <v>23</v>
@@ -7987,7 +7963,7 @@
         <v>23</v>
       </c>
       <c r="L84" t="s">
-        <v>23</v>
+        <v>360</v>
       </c>
       <c r="M84" t="s">
         <v>23</v>
@@ -8005,33 +7981,33 @@
         <v>23</v>
       </c>
       <c r="R84" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="S84">
         <v>0</v>
       </c>
       <c r="T84" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
     </row>
     <row r="85" spans="1:20">
       <c r="A85" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
       <c r="B85" t="s">
-        <v>365</v>
+        <v>362</v>
       </c>
       <c r="C85" t="s">
         <v>20</v>
       </c>
       <c r="D85" t="s">
-        <v>21</v>
+        <v>42</v>
       </c>
       <c r="E85" t="s">
-        <v>174</v>
+        <v>84</v>
       </c>
       <c r="F85" t="s">
-        <v>366</v>
+        <v>363</v>
       </c>
       <c r="G85" t="s">
         <v>23</v>
@@ -8078,10 +8054,10 @@
     </row>
     <row r="86" spans="1:20">
       <c r="A86" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
       <c r="B86" t="s">
-        <v>368</v>
+        <v>365</v>
       </c>
       <c r="C86" t="s">
         <v>20</v>
@@ -8090,10 +8066,10 @@
         <v>21</v>
       </c>
       <c r="E86" t="s">
-        <v>38</v>
+        <v>174</v>
       </c>
       <c r="F86" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="G86" t="s">
         <v>23</v>
@@ -8111,7 +8087,7 @@
         <v>23</v>
       </c>
       <c r="L86" t="s">
-        <v>370</v>
+        <v>23</v>
       </c>
       <c r="M86" t="s">
         <v>23</v>
@@ -8129,21 +8105,21 @@
         <v>23</v>
       </c>
       <c r="R86" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="S86">
         <v>0</v>
       </c>
       <c r="T86" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
     </row>
     <row r="87" spans="1:20">
       <c r="A87" t="s">
-        <v>371</v>
+        <v>367</v>
       </c>
       <c r="B87" t="s">
-        <v>372</v>
+        <v>368</v>
       </c>
       <c r="C87" t="s">
         <v>20</v>
@@ -8152,10 +8128,10 @@
         <v>21</v>
       </c>
       <c r="E87" t="s">
-        <v>64</v>
+        <v>38</v>
       </c>
       <c r="F87" t="s">
-        <v>373</v>
+        <v>369</v>
       </c>
       <c r="G87" t="s">
         <v>23</v>
@@ -8173,7 +8149,7 @@
         <v>23</v>
       </c>
       <c r="L87" t="s">
-        <v>374</v>
+        <v>370</v>
       </c>
       <c r="M87" t="s">
         <v>23</v>
@@ -8202,10 +8178,10 @@
     </row>
     <row r="88" spans="1:20">
       <c r="A88" t="s">
-        <v>376</v>
+        <v>371</v>
       </c>
       <c r="B88" t="s">
-        <v>377</v>
+        <v>372</v>
       </c>
       <c r="C88" t="s">
         <v>20</v>
@@ -8214,10 +8190,10 @@
         <v>21</v>
       </c>
       <c r="E88" t="s">
-        <v>38</v>
+        <v>64</v>
       </c>
       <c r="F88" t="s">
-        <v>378</v>
+        <v>373</v>
       </c>
       <c r="G88" t="s">
         <v>23</v>
@@ -8235,7 +8211,7 @@
         <v>23</v>
       </c>
       <c r="L88" t="s">
-        <v>23</v>
+        <v>374</v>
       </c>
       <c r="M88" t="s">
         <v>23</v>
@@ -8253,21 +8229,21 @@
         <v>23</v>
       </c>
       <c r="R88" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="S88">
         <v>0</v>
       </c>
       <c r="T88" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
     </row>
     <row r="89" spans="1:20">
       <c r="A89" t="s">
-        <v>379</v>
+        <v>376</v>
       </c>
       <c r="B89" t="s">
-        <v>380</v>
+        <v>377</v>
       </c>
       <c r="C89" t="s">
         <v>20</v>
@@ -8276,10 +8252,10 @@
         <v>21</v>
       </c>
       <c r="E89" t="s">
-        <v>22</v>
+        <v>38</v>
       </c>
       <c r="F89" t="s">
-        <v>381</v>
+        <v>378</v>
       </c>
       <c r="G89" t="s">
         <v>23</v>
@@ -8326,22 +8302,22 @@
     </row>
     <row r="90" spans="1:20">
       <c r="A90" t="s">
-        <v>382</v>
+        <v>379</v>
       </c>
       <c r="B90" t="s">
-        <v>383</v>
+        <v>380</v>
       </c>
       <c r="C90" t="s">
         <v>20</v>
       </c>
       <c r="D90" t="s">
-        <v>42</v>
+        <v>21</v>
       </c>
       <c r="E90" t="s">
-        <v>43</v>
+        <v>22</v>
       </c>
       <c r="F90" t="s">
-        <v>384</v>
+        <v>381</v>
       </c>
       <c r="G90" t="s">
         <v>23</v>
@@ -8359,7 +8335,7 @@
         <v>23</v>
       </c>
       <c r="L90" t="s">
-        <v>385</v>
+        <v>23</v>
       </c>
       <c r="M90" t="s">
         <v>23</v>
@@ -8377,33 +8353,33 @@
         <v>23</v>
       </c>
       <c r="R90" t="s">
-        <v>46</v>
+        <v>23</v>
       </c>
       <c r="S90">
         <v>0</v>
       </c>
       <c r="T90" t="s">
-        <v>47</v>
+        <v>23</v>
       </c>
     </row>
     <row r="91" spans="1:20">
       <c r="A91" t="s">
-        <v>386</v>
+        <v>382</v>
       </c>
       <c r="B91" t="s">
-        <v>387</v>
+        <v>383</v>
       </c>
       <c r="C91" t="s">
         <v>20</v>
       </c>
       <c r="D91" t="s">
-        <v>21</v>
+        <v>42</v>
       </c>
       <c r="E91" t="s">
-        <v>388</v>
+        <v>43</v>
       </c>
       <c r="F91" t="s">
-        <v>389</v>
+        <v>384</v>
       </c>
       <c r="G91" t="s">
         <v>23</v>
@@ -8421,7 +8397,7 @@
         <v>23</v>
       </c>
       <c r="L91" t="s">
-        <v>390</v>
+        <v>385</v>
       </c>
       <c r="M91" t="s">
         <v>23</v>
@@ -8439,33 +8415,33 @@
         <v>23</v>
       </c>
       <c r="R91" t="s">
-        <v>29</v>
+        <v>46</v>
       </c>
       <c r="S91">
         <v>0</v>
       </c>
       <c r="T91" t="s">
-        <v>30</v>
+        <v>47</v>
       </c>
     </row>
     <row r="92" spans="1:20">
       <c r="A92" t="s">
-        <v>391</v>
+        <v>386</v>
       </c>
       <c r="B92" t="s">
-        <v>392</v>
+        <v>387</v>
       </c>
       <c r="C92" t="s">
         <v>20</v>
       </c>
       <c r="D92" t="s">
-        <v>42</v>
+        <v>21</v>
       </c>
       <c r="E92" t="s">
-        <v>69</v>
+        <v>388</v>
       </c>
       <c r="F92" t="s">
-        <v>393</v>
+        <v>389</v>
       </c>
       <c r="G92" t="s">
         <v>23</v>
@@ -8483,7 +8459,7 @@
         <v>23</v>
       </c>
       <c r="L92" t="s">
-        <v>23</v>
+        <v>390</v>
       </c>
       <c r="M92" t="s">
         <v>23</v>
@@ -8501,33 +8477,33 @@
         <v>23</v>
       </c>
       <c r="R92" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="S92">
         <v>0</v>
       </c>
       <c r="T92" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
     </row>
     <row r="93" spans="1:20">
       <c r="A93" t="s">
-        <v>394</v>
+        <v>391</v>
       </c>
       <c r="B93" t="s">
-        <v>395</v>
+        <v>392</v>
       </c>
       <c r="C93" t="s">
         <v>20</v>
       </c>
       <c r="D93" t="s">
-        <v>21</v>
+        <v>42</v>
       </c>
       <c r="E93" t="s">
-        <v>38</v>
+        <v>69</v>
       </c>
       <c r="F93" t="s">
-        <v>396</v>
+        <v>393</v>
       </c>
       <c r="G93" t="s">
         <v>23</v>
@@ -8574,10 +8550,10 @@
     </row>
     <row r="94" spans="1:20">
       <c r="A94" t="s">
-        <v>397</v>
+        <v>394</v>
       </c>
       <c r="B94" t="s">
-        <v>398</v>
+        <v>395</v>
       </c>
       <c r="C94" t="s">
         <v>20</v>
@@ -8586,10 +8562,10 @@
         <v>21</v>
       </c>
       <c r="E94" t="s">
-        <v>244</v>
+        <v>38</v>
       </c>
       <c r="F94" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
       <c r="G94" t="s">
         <v>23</v>
@@ -8636,10 +8612,10 @@
     </row>
     <row r="95" spans="1:20">
       <c r="A95" t="s">
-        <v>400</v>
+        <v>397</v>
       </c>
       <c r="B95" t="s">
-        <v>401</v>
+        <v>398</v>
       </c>
       <c r="C95" t="s">
         <v>20</v>
@@ -8648,10 +8624,10 @@
         <v>21</v>
       </c>
       <c r="E95" t="s">
-        <v>402</v>
+        <v>244</v>
       </c>
       <c r="F95" t="s">
-        <v>403</v>
+        <v>399</v>
       </c>
       <c r="G95" t="s">
         <v>23</v>
@@ -8698,22 +8674,22 @@
     </row>
     <row r="96" spans="1:20">
       <c r="A96" t="s">
-        <v>404</v>
+        <v>400</v>
       </c>
       <c r="B96" t="s">
-        <v>405</v>
+        <v>401</v>
       </c>
       <c r="C96" t="s">
         <v>20</v>
       </c>
       <c r="D96" t="s">
-        <v>42</v>
+        <v>21</v>
       </c>
       <c r="E96" t="s">
-        <v>69</v>
+        <v>402</v>
       </c>
       <c r="F96" t="s">
-        <v>406</v>
+        <v>403</v>
       </c>
       <c r="G96" t="s">
         <v>23</v>
@@ -8731,7 +8707,7 @@
         <v>23</v>
       </c>
       <c r="L96" t="s">
-        <v>407</v>
+        <v>23</v>
       </c>
       <c r="M96" t="s">
         <v>23</v>
@@ -8749,33 +8725,33 @@
         <v>23</v>
       </c>
       <c r="R96" t="s">
-        <v>46</v>
+        <v>23</v>
       </c>
       <c r="S96">
         <v>0</v>
       </c>
       <c r="T96" t="s">
-        <v>47</v>
+        <v>23</v>
       </c>
     </row>
     <row r="97" spans="1:20">
       <c r="A97" t="s">
-        <v>408</v>
+        <v>404</v>
       </c>
       <c r="B97" t="s">
-        <v>409</v>
+        <v>405</v>
       </c>
       <c r="C97" t="s">
         <v>20</v>
       </c>
       <c r="D97" t="s">
-        <v>21</v>
+        <v>42</v>
       </c>
       <c r="E97" t="s">
-        <v>22</v>
+        <v>69</v>
       </c>
       <c r="F97" t="s">
-        <v>410</v>
+        <v>406</v>
       </c>
       <c r="G97" t="s">
         <v>23</v>
@@ -8793,7 +8769,7 @@
         <v>23</v>
       </c>
       <c r="L97" t="s">
-        <v>411</v>
+        <v>407</v>
       </c>
       <c r="M97" t="s">
         <v>23</v>
@@ -8811,21 +8787,21 @@
         <v>23</v>
       </c>
       <c r="R97" t="s">
-        <v>29</v>
+        <v>46</v>
       </c>
       <c r="S97">
         <v>0</v>
       </c>
       <c r="T97" t="s">
-        <v>30</v>
+        <v>47</v>
       </c>
     </row>
     <row r="98" spans="1:20">
       <c r="A98" t="s">
-        <v>412</v>
+        <v>408</v>
       </c>
       <c r="B98" t="s">
-        <v>413</v>
+        <v>409</v>
       </c>
       <c r="C98" t="s">
         <v>20</v>
@@ -8834,10 +8810,10 @@
         <v>21</v>
       </c>
       <c r="E98" t="s">
-        <v>209</v>
+        <v>22</v>
       </c>
       <c r="F98" t="s">
-        <v>414</v>
+        <v>410</v>
       </c>
       <c r="G98" t="s">
         <v>23</v>
@@ -8855,7 +8831,7 @@
         <v>23</v>
       </c>
       <c r="L98" t="s">
-        <v>415</v>
+        <v>411</v>
       </c>
       <c r="M98" t="s">
         <v>23</v>
@@ -8884,22 +8860,22 @@
     </row>
     <row r="99" spans="1:20">
       <c r="A99" t="s">
-        <v>416</v>
+        <v>412</v>
       </c>
       <c r="B99" t="s">
-        <v>417</v>
+        <v>413</v>
       </c>
       <c r="C99" t="s">
         <v>20</v>
       </c>
       <c r="D99" t="s">
-        <v>42</v>
+        <v>21</v>
       </c>
       <c r="E99" t="s">
-        <v>47</v>
+        <v>209</v>
       </c>
       <c r="F99" t="s">
-        <v>418</v>
+        <v>414</v>
       </c>
       <c r="G99" t="s">
         <v>23</v>
@@ -8917,7 +8893,7 @@
         <v>23</v>
       </c>
       <c r="L99" t="s">
-        <v>23</v>
+        <v>415</v>
       </c>
       <c r="M99" t="s">
         <v>23</v>
@@ -8935,33 +8911,33 @@
         <v>23</v>
       </c>
       <c r="R99" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="S99">
         <v>0</v>
       </c>
       <c r="T99" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
     </row>
     <row r="100" spans="1:20">
       <c r="A100" t="s">
-        <v>419</v>
+        <v>416</v>
       </c>
       <c r="B100" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
       <c r="C100" t="s">
         <v>20</v>
       </c>
       <c r="D100" t="s">
-        <v>154</v>
+        <v>42</v>
       </c>
       <c r="E100" t="s">
-        <v>421</v>
+        <v>47</v>
       </c>
       <c r="F100" t="s">
-        <v>422</v>
+        <v>418</v>
       </c>
       <c r="G100" t="s">
         <v>23</v>
@@ -9008,22 +8984,22 @@
     </row>
     <row r="101" spans="1:20">
       <c r="A101" t="s">
-        <v>423</v>
+        <v>419</v>
       </c>
       <c r="B101" t="s">
-        <v>424</v>
+        <v>420</v>
       </c>
       <c r="C101" t="s">
         <v>20</v>
       </c>
       <c r="D101" t="s">
-        <v>42</v>
+        <v>154</v>
       </c>
       <c r="E101" t="s">
-        <v>47</v>
+        <v>421</v>
       </c>
       <c r="F101" t="s">
-        <v>425</v>
+        <v>422</v>
       </c>
       <c r="G101" t="s">
         <v>23</v>
@@ -9041,7 +9017,7 @@
         <v>23</v>
       </c>
       <c r="L101" t="s">
-        <v>426</v>
+        <v>23</v>
       </c>
       <c r="M101" t="s">
         <v>23</v>
@@ -9059,33 +9035,33 @@
         <v>23</v>
       </c>
       <c r="R101" t="s">
-        <v>46</v>
+        <v>23</v>
       </c>
       <c r="S101">
         <v>0</v>
       </c>
       <c r="T101" t="s">
-        <v>47</v>
+        <v>23</v>
       </c>
     </row>
     <row r="102" spans="1:20">
       <c r="A102" t="s">
-        <v>427</v>
+        <v>423</v>
       </c>
       <c r="B102" t="s">
-        <v>428</v>
+        <v>424</v>
       </c>
       <c r="C102" t="s">
         <v>20</v>
       </c>
       <c r="D102" t="s">
-        <v>21</v>
+        <v>42</v>
       </c>
       <c r="E102" t="s">
-        <v>429</v>
+        <v>47</v>
       </c>
       <c r="F102" t="s">
-        <v>430</v>
+        <v>425</v>
       </c>
       <c r="G102" t="s">
         <v>23</v>
@@ -9103,7 +9079,7 @@
         <v>23</v>
       </c>
       <c r="L102" t="s">
-        <v>431</v>
+        <v>426</v>
       </c>
       <c r="M102" t="s">
         <v>23</v>
@@ -9121,21 +9097,21 @@
         <v>23</v>
       </c>
       <c r="R102" t="s">
-        <v>29</v>
+        <v>46</v>
       </c>
       <c r="S102">
         <v>0</v>
       </c>
       <c r="T102" t="s">
-        <v>30</v>
+        <v>47</v>
       </c>
     </row>
     <row r="103" spans="1:20">
       <c r="A103" t="s">
-        <v>432</v>
+        <v>427</v>
       </c>
       <c r="B103" t="s">
-        <v>433</v>
+        <v>428</v>
       </c>
       <c r="C103" t="s">
         <v>20</v>
@@ -9144,10 +9120,10 @@
         <v>21</v>
       </c>
       <c r="E103" t="s">
-        <v>434</v>
+        <v>429</v>
       </c>
       <c r="F103" t="s">
-        <v>435</v>
+        <v>430</v>
       </c>
       <c r="G103" t="s">
         <v>23</v>
@@ -9165,7 +9141,7 @@
         <v>23</v>
       </c>
       <c r="L103" t="s">
-        <v>436</v>
+        <v>431</v>
       </c>
       <c r="M103" t="s">
         <v>23</v>
@@ -9194,22 +9170,22 @@
     </row>
     <row r="104" spans="1:20">
       <c r="A104" t="s">
-        <v>437</v>
+        <v>432</v>
       </c>
       <c r="B104" t="s">
-        <v>438</v>
+        <v>433</v>
       </c>
       <c r="C104" t="s">
         <v>20</v>
       </c>
       <c r="D104" t="s">
-        <v>42</v>
+        <v>21</v>
       </c>
       <c r="E104" t="s">
-        <v>439</v>
+        <v>434</v>
       </c>
       <c r="F104" t="s">
-        <v>440</v>
+        <v>435</v>
       </c>
       <c r="G104" t="s">
         <v>23</v>
@@ -9227,7 +9203,7 @@
         <v>23</v>
       </c>
       <c r="L104" t="s">
-        <v>23</v>
+        <v>436</v>
       </c>
       <c r="M104" t="s">
         <v>23</v>
@@ -9245,33 +9221,33 @@
         <v>23</v>
       </c>
       <c r="R104" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="S104">
         <v>0</v>
       </c>
       <c r="T104" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
     </row>
     <row r="105" spans="1:20">
       <c r="A105" t="s">
-        <v>441</v>
+        <v>437</v>
       </c>
       <c r="B105" t="s">
-        <v>442</v>
+        <v>438</v>
       </c>
       <c r="C105" t="s">
         <v>20</v>
       </c>
       <c r="D105" t="s">
-        <v>21</v>
+        <v>42</v>
       </c>
       <c r="E105" t="s">
-        <v>38</v>
+        <v>439</v>
       </c>
       <c r="F105" t="s">
-        <v>443</v>
+        <v>440</v>
       </c>
       <c r="G105" t="s">
         <v>23</v>
@@ -9318,22 +9294,22 @@
     </row>
     <row r="106" spans="1:20">
       <c r="A106" t="s">
-        <v>444</v>
+        <v>441</v>
       </c>
       <c r="B106" t="s">
-        <v>445</v>
+        <v>442</v>
       </c>
       <c r="C106" t="s">
         <v>20</v>
       </c>
       <c r="D106" t="s">
-        <v>42</v>
+        <v>21</v>
       </c>
       <c r="E106" t="s">
-        <v>84</v>
+        <v>38</v>
       </c>
       <c r="F106" t="s">
-        <v>446</v>
+        <v>443</v>
       </c>
       <c r="G106" t="s">
         <v>23</v>
@@ -9380,22 +9356,22 @@
     </row>
     <row r="107" spans="1:20">
       <c r="A107" t="s">
-        <v>447</v>
+        <v>444</v>
       </c>
       <c r="B107" t="s">
-        <v>448</v>
+        <v>445</v>
       </c>
       <c r="C107" t="s">
         <v>20</v>
       </c>
       <c r="D107" t="s">
-        <v>21</v>
+        <v>42</v>
       </c>
       <c r="E107" t="s">
-        <v>64</v>
+        <v>84</v>
       </c>
       <c r="F107" t="s">
-        <v>449</v>
+        <v>446</v>
       </c>
       <c r="G107" t="s">
         <v>23</v>
@@ -9413,7 +9389,7 @@
         <v>23</v>
       </c>
       <c r="L107" t="s">
-        <v>450</v>
+        <v>23</v>
       </c>
       <c r="M107" t="s">
         <v>23</v>
@@ -9431,21 +9407,21 @@
         <v>23</v>
       </c>
       <c r="R107" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="S107">
         <v>0</v>
       </c>
       <c r="T107" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
     </row>
     <row r="108" spans="1:20">
       <c r="A108" t="s">
-        <v>451</v>
+        <v>447</v>
       </c>
       <c r="B108" t="s">
-        <v>452</v>
+        <v>448</v>
       </c>
       <c r="C108" t="s">
         <v>20</v>
@@ -9454,10 +9430,10 @@
         <v>21</v>
       </c>
       <c r="E108" t="s">
-        <v>38</v>
+        <v>64</v>
       </c>
       <c r="F108" t="s">
-        <v>453</v>
+        <v>449</v>
       </c>
       <c r="G108" t="s">
         <v>23</v>
@@ -9475,7 +9451,7 @@
         <v>23</v>
       </c>
       <c r="L108" t="s">
-        <v>454</v>
+        <v>450</v>
       </c>
       <c r="M108" t="s">
         <v>23</v>
@@ -9504,22 +9480,22 @@
     </row>
     <row r="109" spans="1:20">
       <c r="A109" t="s">
-        <v>455</v>
+        <v>451</v>
       </c>
       <c r="B109" t="s">
-        <v>456</v>
+        <v>452</v>
       </c>
       <c r="C109" t="s">
         <v>20</v>
       </c>
       <c r="D109" t="s">
-        <v>42</v>
+        <v>21</v>
       </c>
       <c r="E109" t="s">
-        <v>93</v>
+        <v>38</v>
       </c>
       <c r="F109" t="s">
-        <v>457</v>
+        <v>453</v>
       </c>
       <c r="G109" t="s">
         <v>23</v>
@@ -9537,7 +9513,7 @@
         <v>23</v>
       </c>
       <c r="L109" t="s">
-        <v>23</v>
+        <v>454</v>
       </c>
       <c r="M109" t="s">
         <v>23</v>
@@ -9555,33 +9531,33 @@
         <v>23</v>
       </c>
       <c r="R109" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="S109">
         <v>0</v>
       </c>
       <c r="T109" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
     </row>
     <row r="110" spans="1:20">
       <c r="A110" t="s">
-        <v>458</v>
+        <v>455</v>
       </c>
       <c r="B110" t="s">
-        <v>459</v>
+        <v>456</v>
       </c>
       <c r="C110" t="s">
         <v>20</v>
       </c>
       <c r="D110" t="s">
-        <v>21</v>
+        <v>42</v>
       </c>
       <c r="E110" t="s">
-        <v>38</v>
+        <v>93</v>
       </c>
       <c r="F110" t="s">
-        <v>460</v>
+        <v>457</v>
       </c>
       <c r="G110" t="s">
         <v>23</v>
@@ -9599,7 +9575,7 @@
         <v>23</v>
       </c>
       <c r="L110" t="s">
-        <v>461</v>
+        <v>23</v>
       </c>
       <c r="M110" t="s">
         <v>23</v>
@@ -9617,21 +9593,21 @@
         <v>23</v>
       </c>
       <c r="R110" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="S110">
         <v>0</v>
       </c>
       <c r="T110" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
     </row>
     <row r="111" spans="1:20">
       <c r="A111" t="s">
-        <v>462</v>
+        <v>458</v>
       </c>
       <c r="B111" t="s">
-        <v>463</v>
+        <v>459</v>
       </c>
       <c r="C111" t="s">
         <v>20</v>
@@ -9640,10 +9616,10 @@
         <v>21</v>
       </c>
       <c r="E111" t="s">
-        <v>464</v>
+        <v>38</v>
       </c>
       <c r="F111" t="s">
-        <v>465</v>
+        <v>460</v>
       </c>
       <c r="G111" t="s">
         <v>23</v>
@@ -9661,7 +9637,7 @@
         <v>23</v>
       </c>
       <c r="L111" t="s">
-        <v>466</v>
+        <v>461</v>
       </c>
       <c r="M111" t="s">
         <v>23</v>
@@ -9690,22 +9666,22 @@
     </row>
     <row r="112" spans="1:20">
       <c r="A112" t="s">
-        <v>467</v>
+        <v>462</v>
       </c>
       <c r="B112" t="s">
-        <v>468</v>
+        <v>463</v>
       </c>
       <c r="C112" t="s">
         <v>20</v>
       </c>
       <c r="D112" t="s">
-        <v>42</v>
+        <v>21</v>
       </c>
       <c r="E112" t="s">
-        <v>84</v>
+        <v>464</v>
       </c>
       <c r="F112" t="s">
-        <v>469</v>
+        <v>465</v>
       </c>
       <c r="G112" t="s">
         <v>23</v>
@@ -9723,7 +9699,7 @@
         <v>23</v>
       </c>
       <c r="L112" t="s">
-        <v>23</v>
+        <v>466</v>
       </c>
       <c r="M112" t="s">
         <v>23</v>
@@ -9741,21 +9717,21 @@
         <v>23</v>
       </c>
       <c r="R112" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="S112">
         <v>0</v>
       </c>
       <c r="T112" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
     </row>
     <row r="113" spans="1:20">
       <c r="A113" t="s">
-        <v>470</v>
+        <v>467</v>
       </c>
       <c r="B113" t="s">
-        <v>471</v>
+        <v>468</v>
       </c>
       <c r="C113" t="s">
         <v>20</v>
@@ -9764,10 +9740,10 @@
         <v>42</v>
       </c>
       <c r="E113" t="s">
-        <v>47</v>
+        <v>84</v>
       </c>
       <c r="F113" t="s">
-        <v>472</v>
+        <v>469</v>
       </c>
       <c r="G113" t="s">
         <v>23</v>
@@ -9814,10 +9790,10 @@
     </row>
     <row r="114" spans="1:20">
       <c r="A114" t="s">
-        <v>473</v>
+        <v>470</v>
       </c>
       <c r="B114" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="C114" t="s">
         <v>20</v>
@@ -9829,7 +9805,7 @@
         <v>47</v>
       </c>
       <c r="F114" t="s">
-        <v>475</v>
+        <v>472</v>
       </c>
       <c r="G114" t="s">
         <v>23</v>
@@ -9876,22 +9852,22 @@
     </row>
     <row r="115" spans="1:20">
       <c r="A115" t="s">
-        <v>476</v>
+        <v>473</v>
       </c>
       <c r="B115" t="s">
-        <v>477</v>
+        <v>474</v>
       </c>
       <c r="C115" t="s">
         <v>20</v>
       </c>
       <c r="D115" t="s">
-        <v>21</v>
+        <v>42</v>
       </c>
       <c r="E115" t="s">
-        <v>38</v>
+        <v>47</v>
       </c>
       <c r="F115" t="s">
-        <v>478</v>
+        <v>475</v>
       </c>
       <c r="G115" t="s">
         <v>23</v>
@@ -9909,7 +9885,7 @@
         <v>23</v>
       </c>
       <c r="L115" t="s">
-        <v>479</v>
+        <v>23</v>
       </c>
       <c r="M115" t="s">
         <v>23</v>
@@ -9927,21 +9903,21 @@
         <v>23</v>
       </c>
       <c r="R115" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="S115">
         <v>0</v>
       </c>
       <c r="T115" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
     </row>
     <row r="116" spans="1:20">
       <c r="A116" t="s">
-        <v>480</v>
+        <v>476</v>
       </c>
       <c r="B116" t="s">
-        <v>481</v>
+        <v>477</v>
       </c>
       <c r="C116" t="s">
         <v>20</v>
@@ -9953,7 +9929,7 @@
         <v>38</v>
       </c>
       <c r="F116" t="s">
-        <v>482</v>
+        <v>478</v>
       </c>
       <c r="G116" t="s">
         <v>23</v>
@@ -9971,7 +9947,7 @@
         <v>23</v>
       </c>
       <c r="L116" t="s">
-        <v>23</v>
+        <v>479</v>
       </c>
       <c r="M116" t="s">
         <v>23</v>
@@ -9989,33 +9965,33 @@
         <v>23</v>
       </c>
       <c r="R116" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="S116">
         <v>0</v>
       </c>
       <c r="T116" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
     </row>
     <row r="117" spans="1:20">
       <c r="A117" t="s">
-        <v>483</v>
+        <v>480</v>
       </c>
       <c r="B117" t="s">
-        <v>484</v>
+        <v>481</v>
       </c>
       <c r="C117" t="s">
         <v>20</v>
       </c>
       <c r="D117" t="s">
-        <v>485</v>
+        <v>21</v>
       </c>
       <c r="E117" t="s">
-        <v>486</v>
+        <v>38</v>
       </c>
       <c r="F117" t="s">
-        <v>487</v>
+        <v>482</v>
       </c>
       <c r="G117" t="s">
         <v>23</v>
@@ -10062,22 +10038,22 @@
     </row>
     <row r="118" spans="1:20">
       <c r="A118" t="s">
-        <v>488</v>
+        <v>483</v>
       </c>
       <c r="B118" t="s">
-        <v>489</v>
+        <v>484</v>
       </c>
       <c r="C118" t="s">
         <v>20</v>
       </c>
       <c r="D118" t="s">
-        <v>42</v>
+        <v>485</v>
       </c>
       <c r="E118" t="s">
-        <v>148</v>
+        <v>486</v>
       </c>
       <c r="F118" t="s">
-        <v>490</v>
+        <v>487</v>
       </c>
       <c r="G118" t="s">
         <v>23</v>
@@ -10095,7 +10071,7 @@
         <v>23</v>
       </c>
       <c r="L118" t="s">
-        <v>491</v>
+        <v>23</v>
       </c>
       <c r="M118" t="s">
         <v>23</v>
@@ -10113,33 +10089,33 @@
         <v>23</v>
       </c>
       <c r="R118" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="S118">
         <v>0</v>
       </c>
       <c r="T118" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
     </row>
     <row r="119" spans="1:20">
       <c r="A119" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="B119" t="s">
-        <v>493</v>
+        <v>489</v>
       </c>
       <c r="C119" t="s">
         <v>20</v>
       </c>
       <c r="D119" t="s">
-        <v>21</v>
+        <v>42</v>
       </c>
       <c r="E119" t="s">
-        <v>434</v>
+        <v>148</v>
       </c>
       <c r="F119" t="s">
-        <v>494</v>
+        <v>490</v>
       </c>
       <c r="G119" t="s">
         <v>23</v>
@@ -10157,7 +10133,7 @@
         <v>23</v>
       </c>
       <c r="L119" t="s">
-        <v>23</v>
+        <v>491</v>
       </c>
       <c r="M119" t="s">
         <v>23</v>
@@ -10175,21 +10151,21 @@
         <v>23</v>
       </c>
       <c r="R119" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="S119">
         <v>0</v>
       </c>
       <c r="T119" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
     </row>
     <row r="120" spans="1:20">
       <c r="A120" t="s">
-        <v>495</v>
+        <v>492</v>
       </c>
       <c r="B120" t="s">
-        <v>496</v>
+        <v>493</v>
       </c>
       <c r="C120" t="s">
         <v>20</v>
@@ -10198,10 +10174,10 @@
         <v>21</v>
       </c>
       <c r="E120" t="s">
-        <v>26</v>
+        <v>434</v>
       </c>
       <c r="F120" t="s">
-        <v>497</v>
+        <v>494</v>
       </c>
       <c r="G120" t="s">
         <v>23</v>
@@ -10248,22 +10224,22 @@
     </row>
     <row r="121" spans="1:20">
       <c r="A121" t="s">
-        <v>498</v>
+        <v>495</v>
       </c>
       <c r="B121" t="s">
-        <v>499</v>
+        <v>496</v>
       </c>
       <c r="C121" t="s">
         <v>20</v>
       </c>
       <c r="D121" t="s">
-        <v>42</v>
+        <v>21</v>
       </c>
       <c r="E121" t="s">
-        <v>69</v>
+        <v>26</v>
       </c>
       <c r="F121" t="s">
-        <v>500</v>
+        <v>497</v>
       </c>
       <c r="G121" t="s">
         <v>23</v>
@@ -10310,22 +10286,22 @@
     </row>
     <row r="122" spans="1:20">
       <c r="A122" t="s">
-        <v>501</v>
+        <v>498</v>
       </c>
       <c r="B122" t="s">
-        <v>502</v>
+        <v>499</v>
       </c>
       <c r="C122" t="s">
         <v>20</v>
       </c>
       <c r="D122" t="s">
-        <v>21</v>
+        <v>42</v>
       </c>
       <c r="E122" t="s">
-        <v>38</v>
+        <v>69</v>
       </c>
       <c r="F122" t="s">
-        <v>503</v>
+        <v>500</v>
       </c>
       <c r="G122" t="s">
         <v>23</v>
@@ -10343,7 +10319,7 @@
         <v>23</v>
       </c>
       <c r="L122" t="s">
-        <v>504</v>
+        <v>23</v>
       </c>
       <c r="M122" t="s">
         <v>23</v>
@@ -10361,21 +10337,21 @@
         <v>23</v>
       </c>
       <c r="R122" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="S122">
         <v>0</v>
       </c>
       <c r="T122" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
     </row>
     <row r="123" spans="1:20">
       <c r="A123" t="s">
-        <v>505</v>
+        <v>501</v>
       </c>
       <c r="B123" t="s">
-        <v>506</v>
+        <v>502</v>
       </c>
       <c r="C123" t="s">
         <v>20</v>
@@ -10384,10 +10360,10 @@
         <v>21</v>
       </c>
       <c r="E123" t="s">
-        <v>26</v>
+        <v>38</v>
       </c>
       <c r="F123" t="s">
-        <v>507</v>
+        <v>503</v>
       </c>
       <c r="G123" t="s">
         <v>23</v>
@@ -10405,7 +10381,7 @@
         <v>23</v>
       </c>
       <c r="L123" t="s">
-        <v>508</v>
+        <v>504</v>
       </c>
       <c r="M123" t="s">
         <v>23</v>
@@ -10434,22 +10410,22 @@
     </row>
     <row r="124" spans="1:20">
       <c r="A124" t="s">
-        <v>509</v>
+        <v>505</v>
       </c>
       <c r="B124" t="s">
-        <v>510</v>
+        <v>506</v>
       </c>
       <c r="C124" t="s">
         <v>20</v>
       </c>
       <c r="D124" t="s">
-        <v>42</v>
+        <v>21</v>
       </c>
       <c r="E124" t="s">
-        <v>47</v>
+        <v>26</v>
       </c>
       <c r="F124" t="s">
-        <v>511</v>
+        <v>507</v>
       </c>
       <c r="G124" t="s">
         <v>23</v>
@@ -10467,7 +10443,7 @@
         <v>23</v>
       </c>
       <c r="L124" t="s">
-        <v>23</v>
+        <v>508</v>
       </c>
       <c r="M124" t="s">
         <v>23</v>
@@ -10485,33 +10461,33 @@
         <v>23</v>
       </c>
       <c r="R124" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="S124">
         <v>0</v>
       </c>
       <c r="T124" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
     </row>
     <row r="125" spans="1:20">
       <c r="A125" t="s">
-        <v>512</v>
+        <v>509</v>
       </c>
       <c r="B125" t="s">
-        <v>513</v>
+        <v>510</v>
       </c>
       <c r="C125" t="s">
         <v>20</v>
       </c>
       <c r="D125" t="s">
-        <v>21</v>
+        <v>42</v>
       </c>
       <c r="E125" t="s">
-        <v>38</v>
+        <v>47</v>
       </c>
       <c r="F125" t="s">
-        <v>514</v>
+        <v>511</v>
       </c>
       <c r="G125" t="s">
         <v>23</v>
@@ -10558,10 +10534,10 @@
     </row>
     <row r="126" spans="1:20">
       <c r="A126" t="s">
-        <v>515</v>
+        <v>512</v>
       </c>
       <c r="B126" t="s">
-        <v>516</v>
+        <v>513</v>
       </c>
       <c r="C126" t="s">
         <v>20</v>
@@ -10573,7 +10549,7 @@
         <v>38</v>
       </c>
       <c r="F126" t="s">
-        <v>517</v>
+        <v>514</v>
       </c>
       <c r="G126" t="s">
         <v>23</v>
@@ -10620,22 +10596,22 @@
     </row>
     <row r="127" spans="1:20">
       <c r="A127" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="B127" t="s">
-        <v>519</v>
+        <v>516</v>
       </c>
       <c r="C127" t="s">
         <v>20</v>
       </c>
       <c r="D127" t="s">
-        <v>42</v>
+        <v>21</v>
       </c>
       <c r="E127" t="s">
-        <v>84</v>
+        <v>38</v>
       </c>
       <c r="F127" t="s">
-        <v>520</v>
+        <v>517</v>
       </c>
       <c r="G127" t="s">
         <v>23</v>
@@ -10653,7 +10629,7 @@
         <v>23</v>
       </c>
       <c r="L127" t="s">
-        <v>521</v>
+        <v>23</v>
       </c>
       <c r="M127" t="s">
         <v>23</v>
@@ -10671,21 +10647,21 @@
         <v>23</v>
       </c>
       <c r="R127" t="s">
-        <v>46</v>
+        <v>23</v>
       </c>
       <c r="S127">
         <v>0</v>
       </c>
       <c r="T127" t="s">
-        <v>47</v>
+        <v>23</v>
       </c>
     </row>
     <row r="128" spans="1:20">
       <c r="A128" t="s">
-        <v>522</v>
+        <v>518</v>
       </c>
       <c r="B128" t="s">
-        <v>523</v>
+        <v>519</v>
       </c>
       <c r="C128" t="s">
         <v>20</v>
@@ -10694,60 +10670,60 @@
         <v>42</v>
       </c>
       <c r="E128" t="s">
+        <v>84</v>
+      </c>
+      <c r="F128" t="s">
+        <v>520</v>
+      </c>
+      <c r="G128" t="s">
+        <v>23</v>
+      </c>
+      <c r="H128" t="s">
+        <v>23</v>
+      </c>
+      <c r="I128" t="s">
+        <v>23</v>
+      </c>
+      <c r="J128" t="s">
+        <v>23</v>
+      </c>
+      <c r="K128" t="s">
+        <v>23</v>
+      </c>
+      <c r="L128" t="s">
+        <v>521</v>
+      </c>
+      <c r="M128" t="s">
+        <v>23</v>
+      </c>
+      <c r="N128" t="s">
+        <v>23</v>
+      </c>
+      <c r="O128" t="s">
+        <v>23</v>
+      </c>
+      <c r="P128" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q128" t="s">
+        <v>23</v>
+      </c>
+      <c r="R128" t="s">
+        <v>46</v>
+      </c>
+      <c r="S128">
+        <v>0</v>
+      </c>
+      <c r="T128" t="s">
         <v>47</v>
-      </c>
-      <c r="F128" t="s">
-        <v>524</v>
-      </c>
-      <c r="G128" t="s">
-        <v>23</v>
-      </c>
-      <c r="H128" t="s">
-        <v>23</v>
-      </c>
-      <c r="I128" t="s">
-        <v>23</v>
-      </c>
-      <c r="J128" t="s">
-        <v>23</v>
-      </c>
-      <c r="K128" t="s">
-        <v>23</v>
-      </c>
-      <c r="L128" t="s">
-        <v>23</v>
-      </c>
-      <c r="M128" t="s">
-        <v>23</v>
-      </c>
-      <c r="N128" t="s">
-        <v>23</v>
-      </c>
-      <c r="O128" t="s">
-        <v>23</v>
-      </c>
-      <c r="P128" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q128" t="s">
-        <v>23</v>
-      </c>
-      <c r="R128" t="s">
-        <v>23</v>
-      </c>
-      <c r="S128">
-        <v>0</v>
-      </c>
-      <c r="T128" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="129" spans="1:20">
       <c r="A129" t="s">
-        <v>525</v>
+        <v>522</v>
       </c>
       <c r="B129" t="s">
-        <v>526</v>
+        <v>523</v>
       </c>
       <c r="C129" t="s">
         <v>20</v>
@@ -10756,10 +10732,10 @@
         <v>42</v>
       </c>
       <c r="E129" t="s">
-        <v>276</v>
+        <v>47</v>
       </c>
       <c r="F129" t="s">
-        <v>527</v>
+        <v>524</v>
       </c>
       <c r="G129" t="s">
         <v>23</v>
@@ -10806,22 +10782,22 @@
     </row>
     <row r="130" spans="1:20">
       <c r="A130" t="s">
-        <v>528</v>
+        <v>525</v>
       </c>
       <c r="B130" t="s">
-        <v>529</v>
+        <v>526</v>
       </c>
       <c r="C130" t="s">
         <v>20</v>
       </c>
       <c r="D130" t="s">
-        <v>21</v>
+        <v>42</v>
       </c>
       <c r="E130" t="s">
-        <v>530</v>
+        <v>276</v>
       </c>
       <c r="F130" t="s">
-        <v>531</v>
+        <v>527</v>
       </c>
       <c r="G130" t="s">
         <v>23</v>
@@ -10839,7 +10815,7 @@
         <v>23</v>
       </c>
       <c r="L130" t="s">
-        <v>532</v>
+        <v>23</v>
       </c>
       <c r="M130" t="s">
         <v>23</v>
@@ -10857,33 +10833,33 @@
         <v>23</v>
       </c>
       <c r="R130" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="S130">
         <v>0</v>
       </c>
       <c r="T130" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
     </row>
     <row r="131" spans="1:20">
       <c r="A131" t="s">
-        <v>533</v>
+        <v>528</v>
       </c>
       <c r="B131" t="s">
-        <v>534</v>
+        <v>529</v>
       </c>
       <c r="C131" t="s">
         <v>20</v>
       </c>
       <c r="D131" t="s">
-        <v>42</v>
+        <v>21</v>
       </c>
       <c r="E131" t="s">
-        <v>47</v>
+        <v>530</v>
       </c>
       <c r="F131" t="s">
-        <v>524</v>
+        <v>531</v>
       </c>
       <c r="G131" t="s">
         <v>23</v>
@@ -10901,7 +10877,7 @@
         <v>23</v>
       </c>
       <c r="L131" t="s">
-        <v>23</v>
+        <v>532</v>
       </c>
       <c r="M131" t="s">
         <v>23</v>
@@ -10919,21 +10895,21 @@
         <v>23</v>
       </c>
       <c r="R131" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="S131">
         <v>0</v>
       </c>
       <c r="T131" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
     </row>
     <row r="132" spans="1:20">
       <c r="A132" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
       <c r="B132" t="s">
-        <v>536</v>
+        <v>534</v>
       </c>
       <c r="C132" t="s">
         <v>20</v>
@@ -10942,10 +10918,10 @@
         <v>42</v>
       </c>
       <c r="E132" t="s">
-        <v>84</v>
+        <v>47</v>
       </c>
       <c r="F132" t="s">
-        <v>537</v>
+        <v>524</v>
       </c>
       <c r="G132" t="s">
         <v>23</v>
@@ -10963,7 +10939,7 @@
         <v>23</v>
       </c>
       <c r="L132" t="s">
-        <v>538</v>
+        <v>23</v>
       </c>
       <c r="M132" t="s">
         <v>23</v>
@@ -10981,33 +10957,33 @@
         <v>23</v>
       </c>
       <c r="R132" t="s">
-        <v>46</v>
+        <v>23</v>
       </c>
       <c r="S132">
         <v>0</v>
       </c>
       <c r="T132" t="s">
-        <v>47</v>
+        <v>23</v>
       </c>
     </row>
     <row r="133" spans="1:20">
       <c r="A133" t="s">
-        <v>539</v>
+        <v>535</v>
       </c>
       <c r="B133" t="s">
-        <v>540</v>
+        <v>536</v>
       </c>
       <c r="C133" t="s">
         <v>20</v>
       </c>
       <c r="D133" t="s">
-        <v>21</v>
+        <v>42</v>
       </c>
       <c r="E133" t="s">
-        <v>38</v>
+        <v>84</v>
       </c>
       <c r="F133" t="s">
-        <v>541</v>
+        <v>537</v>
       </c>
       <c r="G133" t="s">
         <v>23</v>
@@ -11025,7 +11001,7 @@
         <v>23</v>
       </c>
       <c r="L133" t="s">
-        <v>23</v>
+        <v>538</v>
       </c>
       <c r="M133" t="s">
         <v>23</v>
@@ -11043,21 +11019,21 @@
         <v>23</v>
       </c>
       <c r="R133" t="s">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="S133">
         <v>0</v>
       </c>
       <c r="T133" t="s">
-        <v>23</v>
+        <v>47</v>
       </c>
     </row>
     <row r="134" spans="1:20">
       <c r="A134" t="s">
-        <v>542</v>
+        <v>539</v>
       </c>
       <c r="B134" t="s">
-        <v>543</v>
+        <v>540</v>
       </c>
       <c r="C134" t="s">
         <v>20</v>
@@ -11066,10 +11042,10 @@
         <v>21</v>
       </c>
       <c r="E134" t="s">
-        <v>22</v>
+        <v>38</v>
       </c>
       <c r="F134" t="s">
-        <v>544</v>
+        <v>541</v>
       </c>
       <c r="G134" t="s">
         <v>23</v>
@@ -11116,10 +11092,10 @@
     </row>
     <row r="135" spans="1:20">
       <c r="A135" t="s">
-        <v>545</v>
+        <v>542</v>
       </c>
       <c r="B135" t="s">
-        <v>546</v>
+        <v>543</v>
       </c>
       <c r="C135" t="s">
         <v>20</v>
@@ -11128,10 +11104,10 @@
         <v>21</v>
       </c>
       <c r="E135" t="s">
-        <v>547</v>
+        <v>22</v>
       </c>
       <c r="F135" t="s">
-        <v>548</v>
+        <v>544</v>
       </c>
       <c r="G135" t="s">
         <v>23</v>
@@ -11149,16 +11125,16 @@
         <v>23</v>
       </c>
       <c r="L135" t="s">
-        <v>549</v>
+        <v>23</v>
       </c>
       <c r="M135" t="s">
-        <v>550</v>
+        <v>23</v>
       </c>
       <c r="N135" t="s">
-        <v>551</v>
+        <v>23</v>
       </c>
       <c r="O135" t="s">
-        <v>552</v>
+        <v>23</v>
       </c>
       <c r="P135" t="s">
         <v>23</v>
@@ -11167,21 +11143,21 @@
         <v>23</v>
       </c>
       <c r="R135" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="S135">
         <v>0</v>
       </c>
       <c r="T135" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
     </row>
     <row r="136" spans="1:20">
       <c r="A136" t="s">
-        <v>553</v>
+        <v>545</v>
       </c>
       <c r="B136" t="s">
-        <v>23</v>
+        <v>546</v>
       </c>
       <c r="C136" t="s">
         <v>20</v>
@@ -11190,10 +11166,10 @@
         <v>21</v>
       </c>
       <c r="E136" t="s">
-        <v>434</v>
+        <v>547</v>
       </c>
       <c r="F136" t="s">
-        <v>23</v>
+        <v>548</v>
       </c>
       <c r="G136" t="s">
         <v>23</v>
@@ -11211,16 +11187,16 @@
         <v>23</v>
       </c>
       <c r="L136" t="s">
-        <v>23</v>
+        <v>549</v>
       </c>
       <c r="M136" t="s">
-        <v>23</v>
+        <v>550</v>
       </c>
       <c r="N136" t="s">
-        <v>23</v>
+        <v>551</v>
       </c>
       <c r="O136" t="s">
-        <v>23</v>
+        <v>552</v>
       </c>
       <c r="P136" t="s">
         <v>23</v>
@@ -11240,22 +11216,22 @@
     </row>
     <row r="137" spans="1:20">
       <c r="A137" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="B137" t="s">
-        <v>555</v>
+        <v>23</v>
       </c>
       <c r="C137" t="s">
         <v>20</v>
       </c>
       <c r="D137" t="s">
-        <v>42</v>
+        <v>21</v>
       </c>
       <c r="E137" t="s">
-        <v>93</v>
+        <v>434</v>
       </c>
       <c r="F137" t="s">
-        <v>556</v>
+        <v>23</v>
       </c>
       <c r="G137" t="s">
         <v>23</v>
@@ -11291,21 +11267,21 @@
         <v>23</v>
       </c>
       <c r="R137" t="s">
-        <v>46</v>
+        <v>29</v>
       </c>
       <c r="S137">
         <v>0</v>
       </c>
       <c r="T137" t="s">
-        <v>47</v>
+        <v>30</v>
       </c>
     </row>
     <row r="138" spans="1:20">
       <c r="A138" t="s">
-        <v>557</v>
+        <v>554</v>
       </c>
       <c r="B138" t="s">
-        <v>558</v>
+        <v>555</v>
       </c>
       <c r="C138" t="s">
         <v>20</v>
@@ -11314,10 +11290,10 @@
         <v>42</v>
       </c>
       <c r="E138" t="s">
-        <v>69</v>
+        <v>93</v>
       </c>
       <c r="F138" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="G138" t="s">
         <v>23</v>
@@ -11335,7 +11311,7 @@
         <v>23</v>
       </c>
       <c r="L138" t="s">
-        <v>560</v>
+        <v>23</v>
       </c>
       <c r="M138" t="s">
         <v>23</v>
@@ -11364,22 +11340,22 @@
     </row>
     <row r="139" spans="1:20">
       <c r="A139" t="s">
-        <v>561</v>
+        <v>557</v>
       </c>
       <c r="B139" t="s">
-        <v>562</v>
+        <v>558</v>
       </c>
       <c r="C139" t="s">
         <v>20</v>
       </c>
       <c r="D139" t="s">
-        <v>21</v>
+        <v>42</v>
       </c>
       <c r="E139" t="s">
-        <v>38</v>
+        <v>69</v>
       </c>
       <c r="F139" t="s">
-        <v>563</v>
+        <v>559</v>
       </c>
       <c r="G139" t="s">
         <v>23</v>
@@ -11397,7 +11373,7 @@
         <v>23</v>
       </c>
       <c r="L139" t="s">
-        <v>564</v>
+        <v>560</v>
       </c>
       <c r="M139" t="s">
         <v>23</v>
@@ -11415,21 +11391,21 @@
         <v>23</v>
       </c>
       <c r="R139" t="s">
-        <v>29</v>
+        <v>46</v>
       </c>
       <c r="S139">
         <v>0</v>
       </c>
       <c r="T139" t="s">
-        <v>30</v>
+        <v>47</v>
       </c>
     </row>
     <row r="140" spans="1:20">
       <c r="A140" t="s">
-        <v>565</v>
+        <v>561</v>
       </c>
       <c r="B140" t="s">
-        <v>566</v>
+        <v>562</v>
       </c>
       <c r="C140" t="s">
         <v>20</v>
@@ -11438,10 +11414,10 @@
         <v>21</v>
       </c>
       <c r="E140" t="s">
-        <v>567</v>
+        <v>38</v>
       </c>
       <c r="F140" t="s">
-        <v>568</v>
+        <v>563</v>
       </c>
       <c r="G140" t="s">
         <v>23</v>
@@ -11459,7 +11435,7 @@
         <v>23</v>
       </c>
       <c r="L140" t="s">
-        <v>569</v>
+        <v>564</v>
       </c>
       <c r="M140" t="s">
         <v>23</v>
@@ -11488,10 +11464,10 @@
     </row>
     <row r="141" spans="1:20">
       <c r="A141" t="s">
-        <v>570</v>
+        <v>565</v>
       </c>
       <c r="B141" t="s">
-        <v>571</v>
+        <v>566</v>
       </c>
       <c r="C141" t="s">
         <v>20</v>
@@ -11500,10 +11476,10 @@
         <v>21</v>
       </c>
       <c r="E141" t="s">
-        <v>299</v>
+        <v>567</v>
       </c>
       <c r="F141" t="s">
-        <v>572</v>
+        <v>568</v>
       </c>
       <c r="G141" t="s">
         <v>23</v>
@@ -11521,7 +11497,7 @@
         <v>23</v>
       </c>
       <c r="L141" t="s">
-        <v>573</v>
+        <v>569</v>
       </c>
       <c r="M141" t="s">
         <v>23</v>
@@ -11550,22 +11526,22 @@
     </row>
     <row r="142" spans="1:20">
       <c r="A142" t="s">
-        <v>574</v>
+        <v>570</v>
       </c>
       <c r="B142" t="s">
-        <v>575</v>
+        <v>571</v>
       </c>
       <c r="C142" t="s">
         <v>20</v>
       </c>
       <c r="D142" t="s">
-        <v>42</v>
+        <v>21</v>
       </c>
       <c r="E142" t="s">
-        <v>148</v>
+        <v>299</v>
       </c>
       <c r="F142" t="s">
-        <v>576</v>
+        <v>572</v>
       </c>
       <c r="G142" t="s">
         <v>23</v>
@@ -11583,7 +11559,7 @@
         <v>23</v>
       </c>
       <c r="L142" t="s">
-        <v>577</v>
+        <v>573</v>
       </c>
       <c r="M142" t="s">
         <v>23</v>
@@ -11601,21 +11577,21 @@
         <v>23</v>
       </c>
       <c r="R142" t="s">
-        <v>46</v>
+        <v>29</v>
       </c>
       <c r="S142">
         <v>0</v>
       </c>
       <c r="T142" t="s">
-        <v>47</v>
+        <v>30</v>
       </c>
     </row>
     <row r="143" spans="1:20">
       <c r="A143" t="s">
-        <v>578</v>
+        <v>574</v>
       </c>
       <c r="B143" t="s">
-        <v>579</v>
+        <v>575</v>
       </c>
       <c r="C143" t="s">
         <v>20</v>
@@ -11624,10 +11600,10 @@
         <v>42</v>
       </c>
       <c r="E143" t="s">
-        <v>69</v>
+        <v>148</v>
       </c>
       <c r="F143" t="s">
-        <v>580</v>
+        <v>576</v>
       </c>
       <c r="G143" t="s">
         <v>23</v>
@@ -11645,7 +11621,7 @@
         <v>23</v>
       </c>
       <c r="L143" t="s">
-        <v>581</v>
+        <v>577</v>
       </c>
       <c r="M143" t="s">
         <v>23</v>
@@ -11674,22 +11650,22 @@
     </row>
     <row r="144" spans="1:20">
       <c r="A144" t="s">
-        <v>582</v>
+        <v>578</v>
       </c>
       <c r="B144" t="s">
-        <v>583</v>
+        <v>579</v>
       </c>
       <c r="C144" t="s">
         <v>20</v>
       </c>
       <c r="D144" t="s">
-        <v>21</v>
+        <v>42</v>
       </c>
       <c r="E144" t="s">
-        <v>584</v>
+        <v>69</v>
       </c>
       <c r="F144" t="s">
-        <v>585</v>
+        <v>580</v>
       </c>
       <c r="G144" t="s">
         <v>23</v>
@@ -11707,7 +11683,7 @@
         <v>23</v>
       </c>
       <c r="L144" t="s">
-        <v>586</v>
+        <v>581</v>
       </c>
       <c r="M144" t="s">
         <v>23</v>
@@ -11725,21 +11701,21 @@
         <v>23</v>
       </c>
       <c r="R144" t="s">
-        <v>29</v>
+        <v>46</v>
       </c>
       <c r="S144">
         <v>0</v>
       </c>
       <c r="T144" t="s">
-        <v>30</v>
+        <v>47</v>
       </c>
     </row>
     <row r="145" spans="1:20">
       <c r="A145" t="s">
-        <v>587</v>
+        <v>582</v>
       </c>
       <c r="B145" t="s">
-        <v>588</v>
+        <v>583</v>
       </c>
       <c r="C145" t="s">
         <v>20</v>
@@ -11748,10 +11724,10 @@
         <v>21</v>
       </c>
       <c r="E145" t="s">
-        <v>38</v>
+        <v>584</v>
       </c>
       <c r="F145" t="s">
-        <v>589</v>
+        <v>585</v>
       </c>
       <c r="G145" t="s">
         <v>23</v>
@@ -11769,7 +11745,7 @@
         <v>23</v>
       </c>
       <c r="L145" t="s">
-        <v>590</v>
+        <v>586</v>
       </c>
       <c r="M145" t="s">
         <v>23</v>
@@ -11798,10 +11774,10 @@
     </row>
     <row r="146" spans="1:20">
       <c r="A146" t="s">
-        <v>591</v>
+        <v>587</v>
       </c>
       <c r="B146" t="s">
-        <v>592</v>
+        <v>588</v>
       </c>
       <c r="C146" t="s">
         <v>20</v>
@@ -11813,7 +11789,7 @@
         <v>38</v>
       </c>
       <c r="F146" t="s">
-        <v>593</v>
+        <v>589</v>
       </c>
       <c r="G146" t="s">
         <v>23</v>
@@ -11831,7 +11807,7 @@
         <v>23</v>
       </c>
       <c r="L146" t="s">
-        <v>594</v>
+        <v>590</v>
       </c>
       <c r="M146" t="s">
         <v>23</v>
@@ -11860,10 +11836,10 @@
     </row>
     <row r="147" spans="1:20">
       <c r="A147" t="s">
-        <v>595</v>
+        <v>591</v>
       </c>
       <c r="B147" t="s">
-        <v>596</v>
+        <v>592</v>
       </c>
       <c r="C147" t="s">
         <v>20</v>
@@ -11872,10 +11848,10 @@
         <v>21</v>
       </c>
       <c r="E147" t="s">
-        <v>597</v>
+        <v>38</v>
       </c>
       <c r="F147" t="s">
-        <v>598</v>
+        <v>593</v>
       </c>
       <c r="G147" t="s">
         <v>23</v>
@@ -11893,7 +11869,7 @@
         <v>23</v>
       </c>
       <c r="L147" t="s">
-        <v>599</v>
+        <v>594</v>
       </c>
       <c r="M147" t="s">
         <v>23</v>
@@ -11922,10 +11898,10 @@
     </row>
     <row r="148" spans="1:20">
       <c r="A148" t="s">
-        <v>600</v>
+        <v>595</v>
       </c>
       <c r="B148" t="s">
-        <v>601</v>
+        <v>596</v>
       </c>
       <c r="C148" t="s">
         <v>20</v>
@@ -11934,10 +11910,10 @@
         <v>21</v>
       </c>
       <c r="E148" t="s">
-        <v>108</v>
+        <v>597</v>
       </c>
       <c r="F148" t="s">
-        <v>326</v>
+        <v>598</v>
       </c>
       <c r="G148" t="s">
         <v>23</v>
@@ -11955,7 +11931,7 @@
         <v>23</v>
       </c>
       <c r="L148" t="s">
-        <v>602</v>
+        <v>599</v>
       </c>
       <c r="M148" t="s">
         <v>23</v>
@@ -11984,22 +11960,22 @@
     </row>
     <row r="149" spans="1:20">
       <c r="A149" t="s">
-        <v>603</v>
+        <v>600</v>
       </c>
       <c r="B149" t="s">
-        <v>604</v>
+        <v>601</v>
       </c>
       <c r="C149" t="s">
         <v>20</v>
       </c>
       <c r="D149" t="s">
-        <v>42</v>
+        <v>21</v>
       </c>
       <c r="E149" t="s">
-        <v>143</v>
+        <v>108</v>
       </c>
       <c r="F149" t="s">
-        <v>605</v>
+        <v>326</v>
       </c>
       <c r="G149" t="s">
         <v>23</v>
@@ -12017,7 +11993,7 @@
         <v>23</v>
       </c>
       <c r="L149" t="s">
-        <v>606</v>
+        <v>602</v>
       </c>
       <c r="M149" t="s">
         <v>23</v>
@@ -12035,33 +12011,33 @@
         <v>23</v>
       </c>
       <c r="R149" t="s">
-        <v>46</v>
+        <v>29</v>
       </c>
       <c r="S149">
         <v>0</v>
       </c>
       <c r="T149" t="s">
-        <v>47</v>
+        <v>30</v>
       </c>
     </row>
     <row r="150" spans="1:20">
       <c r="A150" t="s">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="B150" t="s">
-        <v>608</v>
+        <v>604</v>
       </c>
       <c r="C150" t="s">
         <v>20</v>
       </c>
       <c r="D150" t="s">
-        <v>375</v>
+        <v>42</v>
       </c>
       <c r="E150" t="s">
-        <v>609</v>
+        <v>143</v>
       </c>
       <c r="F150" t="s">
-        <v>610</v>
+        <v>605</v>
       </c>
       <c r="G150" t="s">
         <v>23</v>
@@ -12079,7 +12055,7 @@
         <v>23</v>
       </c>
       <c r="L150" t="s">
-        <v>611</v>
+        <v>606</v>
       </c>
       <c r="M150" t="s">
         <v>23</v>
@@ -12097,33 +12073,33 @@
         <v>23</v>
       </c>
       <c r="R150" t="s">
-        <v>612</v>
+        <v>46</v>
       </c>
       <c r="S150">
         <v>0</v>
       </c>
       <c r="T150" t="s">
-        <v>613</v>
+        <v>47</v>
       </c>
     </row>
     <row r="151" spans="1:20">
       <c r="A151" t="s">
-        <v>614</v>
+        <v>607</v>
       </c>
       <c r="B151" t="s">
-        <v>615</v>
+        <v>608</v>
       </c>
       <c r="C151" t="s">
         <v>20</v>
       </c>
       <c r="D151" t="s">
-        <v>42</v>
+        <v>375</v>
       </c>
       <c r="E151" t="s">
-        <v>616</v>
+        <v>609</v>
       </c>
       <c r="F151" t="s">
-        <v>617</v>
+        <v>610</v>
       </c>
       <c r="G151" t="s">
         <v>23</v>
@@ -12141,7 +12117,7 @@
         <v>23</v>
       </c>
       <c r="L151" t="s">
-        <v>618</v>
+        <v>611</v>
       </c>
       <c r="M151" t="s">
         <v>23</v>
@@ -12159,33 +12135,33 @@
         <v>23</v>
       </c>
       <c r="R151" t="s">
-        <v>46</v>
+        <v>612</v>
       </c>
       <c r="S151">
         <v>0</v>
       </c>
       <c r="T151" t="s">
-        <v>47</v>
+        <v>613</v>
       </c>
     </row>
     <row r="152" spans="1:20">
       <c r="A152" t="s">
-        <v>619</v>
+        <v>614</v>
       </c>
       <c r="B152" t="s">
-        <v>620</v>
+        <v>615</v>
       </c>
       <c r="C152" t="s">
         <v>20</v>
       </c>
       <c r="D152" t="s">
-        <v>21</v>
+        <v>42</v>
       </c>
       <c r="E152" t="s">
-        <v>621</v>
+        <v>616</v>
       </c>
       <c r="F152" t="s">
-        <v>622</v>
+        <v>617</v>
       </c>
       <c r="G152" t="s">
         <v>23</v>
@@ -12203,7 +12179,7 @@
         <v>23</v>
       </c>
       <c r="L152" t="s">
-        <v>623</v>
+        <v>618</v>
       </c>
       <c r="M152" t="s">
         <v>23</v>
@@ -12221,33 +12197,33 @@
         <v>23</v>
       </c>
       <c r="R152" t="s">
-        <v>29</v>
+        <v>46</v>
       </c>
       <c r="S152">
         <v>0</v>
       </c>
       <c r="T152" t="s">
-        <v>30</v>
+        <v>47</v>
       </c>
     </row>
     <row r="153" spans="1:20">
       <c r="A153" t="s">
-        <v>624</v>
+        <v>619</v>
       </c>
       <c r="B153" t="s">
-        <v>625</v>
+        <v>620</v>
       </c>
       <c r="C153" t="s">
         <v>20</v>
       </c>
       <c r="D153" t="s">
-        <v>42</v>
+        <v>21</v>
       </c>
       <c r="E153" t="s">
-        <v>47</v>
+        <v>621</v>
       </c>
       <c r="F153" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="G153" t="s">
         <v>23</v>
@@ -12265,7 +12241,7 @@
         <v>23</v>
       </c>
       <c r="L153" t="s">
-        <v>627</v>
+        <v>623</v>
       </c>
       <c r="M153" t="s">
         <v>23</v>
@@ -12283,33 +12259,33 @@
         <v>23</v>
       </c>
       <c r="R153" t="s">
-        <v>46</v>
+        <v>29</v>
       </c>
       <c r="S153">
         <v>0</v>
       </c>
       <c r="T153" t="s">
-        <v>47</v>
+        <v>30</v>
       </c>
     </row>
     <row r="154" spans="1:20">
       <c r="A154" t="s">
-        <v>628</v>
+        <v>624</v>
       </c>
       <c r="B154" t="s">
-        <v>629</v>
+        <v>625</v>
       </c>
       <c r="C154" t="s">
         <v>20</v>
       </c>
       <c r="D154" t="s">
-        <v>21</v>
+        <v>42</v>
       </c>
       <c r="E154" t="s">
-        <v>630</v>
+        <v>47</v>
       </c>
       <c r="F154" t="s">
-        <v>631</v>
+        <v>626</v>
       </c>
       <c r="G154" t="s">
         <v>23</v>
@@ -12327,7 +12303,7 @@
         <v>23</v>
       </c>
       <c r="L154" t="s">
-        <v>632</v>
+        <v>627</v>
       </c>
       <c r="M154" t="s">
         <v>23</v>
@@ -12345,33 +12321,33 @@
         <v>23</v>
       </c>
       <c r="R154" t="s">
-        <v>29</v>
+        <v>46</v>
       </c>
       <c r="S154">
         <v>0</v>
       </c>
       <c r="T154" t="s">
-        <v>30</v>
+        <v>47</v>
       </c>
     </row>
     <row r="155" spans="1:20">
       <c r="A155" t="s">
-        <v>633</v>
+        <v>628</v>
       </c>
       <c r="B155" t="s">
-        <v>634</v>
+        <v>629</v>
       </c>
       <c r="C155" t="s">
         <v>20</v>
       </c>
       <c r="D155" t="s">
-        <v>42</v>
+        <v>21</v>
       </c>
       <c r="E155" t="s">
-        <v>635</v>
+        <v>630</v>
       </c>
       <c r="F155" t="s">
-        <v>636</v>
+        <v>631</v>
       </c>
       <c r="G155" t="s">
         <v>23</v>
@@ -12389,7 +12365,7 @@
         <v>23</v>
       </c>
       <c r="L155" t="s">
-        <v>637</v>
+        <v>632</v>
       </c>
       <c r="M155" t="s">
         <v>23</v>
@@ -12407,33 +12383,33 @@
         <v>23</v>
       </c>
       <c r="R155" t="s">
-        <v>46</v>
+        <v>29</v>
       </c>
       <c r="S155">
         <v>0</v>
       </c>
       <c r="T155" t="s">
-        <v>47</v>
+        <v>30</v>
       </c>
     </row>
     <row r="156" spans="1:20">
       <c r="A156" t="s">
-        <v>638</v>
+        <v>633</v>
       </c>
       <c r="B156" t="s">
-        <v>639</v>
+        <v>634</v>
       </c>
       <c r="C156" t="s">
         <v>20</v>
       </c>
       <c r="D156" t="s">
-        <v>21</v>
+        <v>42</v>
       </c>
       <c r="E156" t="s">
-        <v>640</v>
+        <v>635</v>
       </c>
       <c r="F156" t="s">
-        <v>641</v>
+        <v>636</v>
       </c>
       <c r="G156" t="s">
         <v>23</v>
@@ -12451,7 +12427,7 @@
         <v>23</v>
       </c>
       <c r="L156" t="s">
-        <v>642</v>
+        <v>637</v>
       </c>
       <c r="M156" t="s">
         <v>23</v>
@@ -12469,21 +12445,21 @@
         <v>23</v>
       </c>
       <c r="R156" t="s">
-        <v>29</v>
+        <v>46</v>
       </c>
       <c r="S156">
         <v>0</v>
       </c>
       <c r="T156" t="s">
-        <v>30</v>
+        <v>47</v>
       </c>
     </row>
     <row r="157" spans="1:20">
       <c r="A157" t="s">
-        <v>643</v>
+        <v>638</v>
       </c>
       <c r="B157" t="s">
-        <v>644</v>
+        <v>639</v>
       </c>
       <c r="C157" t="s">
         <v>20</v>
@@ -12492,10 +12468,10 @@
         <v>21</v>
       </c>
       <c r="E157" t="s">
-        <v>26</v>
+        <v>640</v>
       </c>
       <c r="F157" t="s">
-        <v>645</v>
+        <v>641</v>
       </c>
       <c r="G157" t="s">
         <v>23</v>
@@ -12513,7 +12489,7 @@
         <v>23</v>
       </c>
       <c r="L157" t="s">
-        <v>646</v>
+        <v>642</v>
       </c>
       <c r="M157" t="s">
         <v>23</v>
@@ -12542,10 +12518,10 @@
     </row>
     <row r="158" spans="1:20">
       <c r="A158" t="s">
-        <v>647</v>
+        <v>643</v>
       </c>
       <c r="B158" t="s">
-        <v>648</v>
+        <v>644</v>
       </c>
       <c r="C158" t="s">
         <v>20</v>
@@ -12554,10 +12530,10 @@
         <v>21</v>
       </c>
       <c r="E158" t="s">
-        <v>244</v>
+        <v>26</v>
       </c>
       <c r="F158" t="s">
-        <v>649</v>
+        <v>645</v>
       </c>
       <c r="G158" t="s">
         <v>23</v>
@@ -12575,7 +12551,7 @@
         <v>23</v>
       </c>
       <c r="L158" t="s">
-        <v>650</v>
+        <v>646</v>
       </c>
       <c r="M158" t="s">
         <v>23</v>
@@ -12593,33 +12569,33 @@
         <v>23</v>
       </c>
       <c r="R158" t="s">
-        <v>612</v>
+        <v>29</v>
       </c>
       <c r="S158">
         <v>0</v>
       </c>
       <c r="T158" t="s">
-        <v>613</v>
+        <v>30</v>
       </c>
     </row>
     <row r="159" spans="1:20">
       <c r="A159" t="s">
-        <v>651</v>
+        <v>647</v>
       </c>
       <c r="B159" t="s">
-        <v>652</v>
+        <v>648</v>
       </c>
       <c r="C159" t="s">
         <v>20</v>
       </c>
       <c r="D159" t="s">
-        <v>42</v>
+        <v>21</v>
       </c>
       <c r="E159" t="s">
-        <v>653</v>
+        <v>244</v>
       </c>
       <c r="F159" t="s">
-        <v>654</v>
+        <v>649</v>
       </c>
       <c r="G159" t="s">
         <v>23</v>
@@ -12637,7 +12613,7 @@
         <v>23</v>
       </c>
       <c r="L159" t="s">
-        <v>655</v>
+        <v>650</v>
       </c>
       <c r="M159" t="s">
         <v>23</v>
@@ -12655,33 +12631,33 @@
         <v>23</v>
       </c>
       <c r="R159" t="s">
-        <v>46</v>
+        <v>612</v>
       </c>
       <c r="S159">
         <v>0</v>
       </c>
       <c r="T159" t="s">
-        <v>47</v>
+        <v>613</v>
       </c>
     </row>
     <row r="160" spans="1:20">
       <c r="A160" t="s">
-        <v>656</v>
+        <v>651</v>
       </c>
       <c r="B160" t="s">
-        <v>657</v>
+        <v>652</v>
       </c>
       <c r="C160" t="s">
         <v>20</v>
       </c>
       <c r="D160" t="s">
-        <v>21</v>
+        <v>42</v>
       </c>
       <c r="E160" t="s">
-        <v>88</v>
+        <v>653</v>
       </c>
       <c r="F160" t="s">
-        <v>658</v>
+        <v>654</v>
       </c>
       <c r="G160" t="s">
         <v>23</v>
@@ -12699,7 +12675,7 @@
         <v>23</v>
       </c>
       <c r="L160" t="s">
-        <v>659</v>
+        <v>655</v>
       </c>
       <c r="M160" t="s">
         <v>23</v>
@@ -12717,21 +12693,21 @@
         <v>23</v>
       </c>
       <c r="R160" t="s">
-        <v>29</v>
+        <v>46</v>
       </c>
       <c r="S160">
         <v>0</v>
       </c>
       <c r="T160" t="s">
-        <v>30</v>
+        <v>47</v>
       </c>
     </row>
     <row r="161" spans="1:20">
       <c r="A161" t="s">
-        <v>660</v>
+        <v>656</v>
       </c>
       <c r="B161" t="s">
-        <v>661</v>
+        <v>657</v>
       </c>
       <c r="C161" t="s">
         <v>20</v>
@@ -12740,10 +12716,10 @@
         <v>21</v>
       </c>
       <c r="E161" t="s">
-        <v>138</v>
+        <v>88</v>
       </c>
       <c r="F161" t="s">
-        <v>662</v>
+        <v>658</v>
       </c>
       <c r="G161" t="s">
         <v>23</v>
@@ -12761,7 +12737,7 @@
         <v>23</v>
       </c>
       <c r="L161" t="s">
-        <v>663</v>
+        <v>659</v>
       </c>
       <c r="M161" t="s">
         <v>23</v>
@@ -12790,10 +12766,10 @@
     </row>
     <row r="162" spans="1:20">
       <c r="A162" t="s">
-        <v>664</v>
+        <v>660</v>
       </c>
       <c r="B162" t="s">
-        <v>665</v>
+        <v>661</v>
       </c>
       <c r="C162" t="s">
         <v>20</v>
@@ -12802,10 +12778,10 @@
         <v>21</v>
       </c>
       <c r="E162" t="s">
-        <v>38</v>
+        <v>138</v>
       </c>
       <c r="F162" t="s">
-        <v>541</v>
+        <v>662</v>
       </c>
       <c r="G162" t="s">
         <v>23</v>
@@ -12823,7 +12799,7 @@
         <v>23</v>
       </c>
       <c r="L162" t="s">
-        <v>666</v>
+        <v>663</v>
       </c>
       <c r="M162" t="s">
         <v>23</v>
@@ -12852,10 +12828,10 @@
     </row>
     <row r="163" spans="1:20">
       <c r="A163" t="s">
-        <v>667</v>
+        <v>664</v>
       </c>
       <c r="B163" t="s">
-        <v>668</v>
+        <v>665</v>
       </c>
       <c r="C163" t="s">
         <v>20</v>
@@ -12867,7 +12843,7 @@
         <v>38</v>
       </c>
       <c r="F163" t="s">
-        <v>669</v>
+        <v>541</v>
       </c>
       <c r="G163" t="s">
         <v>23</v>
@@ -12885,7 +12861,7 @@
         <v>23</v>
       </c>
       <c r="L163" t="s">
-        <v>670</v>
+        <v>666</v>
       </c>
       <c r="M163" t="s">
         <v>23</v>
@@ -12914,22 +12890,22 @@
     </row>
     <row r="164" spans="1:20">
       <c r="A164" t="s">
-        <v>671</v>
+        <v>667</v>
       </c>
       <c r="B164" t="s">
-        <v>672</v>
+        <v>668</v>
       </c>
       <c r="C164" t="s">
         <v>20</v>
       </c>
       <c r="D164" t="s">
-        <v>42</v>
+        <v>21</v>
       </c>
       <c r="E164" t="s">
-        <v>84</v>
+        <v>38</v>
       </c>
       <c r="F164" t="s">
-        <v>673</v>
+        <v>669</v>
       </c>
       <c r="G164" t="s">
         <v>23</v>
@@ -12947,7 +12923,7 @@
         <v>23</v>
       </c>
       <c r="L164" t="s">
-        <v>674</v>
+        <v>670</v>
       </c>
       <c r="M164" t="s">
         <v>23</v>
@@ -12965,33 +12941,33 @@
         <v>23</v>
       </c>
       <c r="R164" t="s">
-        <v>46</v>
+        <v>29</v>
       </c>
       <c r="S164">
         <v>0</v>
       </c>
       <c r="T164" t="s">
-        <v>47</v>
+        <v>30</v>
       </c>
     </row>
     <row r="165" spans="1:20">
       <c r="A165" t="s">
-        <v>675</v>
+        <v>671</v>
       </c>
       <c r="B165" t="s">
-        <v>676</v>
+        <v>672</v>
       </c>
       <c r="C165" t="s">
         <v>20</v>
       </c>
       <c r="D165" t="s">
-        <v>21</v>
+        <v>42</v>
       </c>
       <c r="E165" t="s">
-        <v>22</v>
+        <v>84</v>
       </c>
       <c r="F165" t="s">
-        <v>677</v>
+        <v>673</v>
       </c>
       <c r="G165" t="s">
         <v>23</v>
@@ -13009,7 +12985,7 @@
         <v>23</v>
       </c>
       <c r="L165" t="s">
-        <v>678</v>
+        <v>674</v>
       </c>
       <c r="M165" t="s">
         <v>23</v>
@@ -13027,33 +13003,33 @@
         <v>23</v>
       </c>
       <c r="R165" t="s">
-        <v>612</v>
+        <v>46</v>
       </c>
       <c r="S165">
         <v>0</v>
       </c>
       <c r="T165" t="s">
-        <v>613</v>
+        <v>47</v>
       </c>
     </row>
     <row r="166" spans="1:20">
       <c r="A166" t="s">
-        <v>679</v>
+        <v>675</v>
       </c>
       <c r="B166" t="s">
-        <v>680</v>
+        <v>676</v>
       </c>
       <c r="C166" t="s">
         <v>20</v>
       </c>
       <c r="D166" t="s">
-        <v>42</v>
+        <v>21</v>
       </c>
       <c r="E166" t="s">
-        <v>47</v>
+        <v>22</v>
       </c>
       <c r="F166" t="s">
-        <v>681</v>
+        <v>677</v>
       </c>
       <c r="G166" t="s">
         <v>23</v>
@@ -13071,7 +13047,7 @@
         <v>23</v>
       </c>
       <c r="L166" t="s">
-        <v>682</v>
+        <v>678</v>
       </c>
       <c r="M166" t="s">
         <v>23</v>
@@ -13089,33 +13065,33 @@
         <v>23</v>
       </c>
       <c r="R166" t="s">
-        <v>46</v>
+        <v>612</v>
       </c>
       <c r="S166">
         <v>0</v>
       </c>
       <c r="T166" t="s">
-        <v>47</v>
+        <v>613</v>
       </c>
     </row>
     <row r="167" spans="1:20">
       <c r="A167" t="s">
-        <v>683</v>
+        <v>679</v>
       </c>
       <c r="B167" t="s">
-        <v>684</v>
+        <v>680</v>
       </c>
       <c r="C167" t="s">
         <v>20</v>
       </c>
       <c r="D167" t="s">
-        <v>21</v>
+        <v>42</v>
       </c>
       <c r="E167" t="s">
-        <v>174</v>
+        <v>47</v>
       </c>
       <c r="F167" t="s">
-        <v>548</v>
+        <v>681</v>
       </c>
       <c r="G167" t="s">
         <v>23</v>
@@ -13133,7 +13109,7 @@
         <v>23</v>
       </c>
       <c r="L167" t="s">
-        <v>685</v>
+        <v>682</v>
       </c>
       <c r="M167" t="s">
         <v>23</v>
@@ -13151,33 +13127,33 @@
         <v>23</v>
       </c>
       <c r="R167" t="s">
-        <v>612</v>
+        <v>46</v>
       </c>
       <c r="S167">
         <v>0</v>
       </c>
       <c r="T167" t="s">
-        <v>613</v>
+        <v>47</v>
       </c>
     </row>
     <row r="168" spans="1:20">
       <c r="A168" t="s">
-        <v>686</v>
+        <v>683</v>
       </c>
       <c r="B168" t="s">
-        <v>687</v>
+        <v>684</v>
       </c>
       <c r="C168" t="s">
         <v>20</v>
       </c>
       <c r="D168" t="s">
-        <v>42</v>
+        <v>21</v>
       </c>
       <c r="E168" t="s">
-        <v>148</v>
+        <v>174</v>
       </c>
       <c r="F168" t="s">
-        <v>688</v>
+        <v>548</v>
       </c>
       <c r="G168" t="s">
         <v>23</v>
@@ -13195,7 +13171,7 @@
         <v>23</v>
       </c>
       <c r="L168" t="s">
-        <v>689</v>
+        <v>685</v>
       </c>
       <c r="M168" t="s">
         <v>23</v>
@@ -13213,21 +13189,21 @@
         <v>23</v>
       </c>
       <c r="R168" t="s">
-        <v>46</v>
+        <v>612</v>
       </c>
       <c r="S168">
         <v>0</v>
       </c>
       <c r="T168" t="s">
-        <v>47</v>
+        <v>613</v>
       </c>
     </row>
     <row r="169" spans="1:20">
       <c r="A169" t="s">
-        <v>123</v>
+        <v>686</v>
       </c>
       <c r="B169" t="s">
-        <v>690</v>
+        <v>687</v>
       </c>
       <c r="C169" t="s">
         <v>20</v>
@@ -13236,10 +13212,10 @@
         <v>42</v>
       </c>
       <c r="E169" t="s">
-        <v>84</v>
+        <v>148</v>
       </c>
       <c r="F169" t="s">
-        <v>247</v>
+        <v>688</v>
       </c>
       <c r="G169" t="s">
         <v>23</v>
@@ -13257,7 +13233,7 @@
         <v>23</v>
       </c>
       <c r="L169" t="s">
-        <v>126</v>
+        <v>689</v>
       </c>
       <c r="M169" t="s">
         <v>23</v>
@@ -13286,22 +13262,22 @@
     </row>
     <row r="170" spans="1:20">
       <c r="A170" t="s">
-        <v>691</v>
+        <v>123</v>
       </c>
       <c r="B170" t="s">
-        <v>692</v>
+        <v>690</v>
       </c>
       <c r="C170" t="s">
         <v>20</v>
       </c>
       <c r="D170" t="s">
-        <v>21</v>
+        <v>42</v>
       </c>
       <c r="E170" t="s">
-        <v>38</v>
+        <v>84</v>
       </c>
       <c r="F170" t="s">
-        <v>693</v>
+        <v>247</v>
       </c>
       <c r="G170" t="s">
         <v>23</v>
@@ -13319,7 +13295,7 @@
         <v>23</v>
       </c>
       <c r="L170" t="s">
-        <v>23</v>
+        <v>126</v>
       </c>
       <c r="M170" t="s">
         <v>23</v>
@@ -13337,21 +13313,21 @@
         <v>23</v>
       </c>
       <c r="R170" t="s">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="S170">
         <v>0</v>
       </c>
       <c r="T170" t="s">
-        <v>23</v>
+        <v>47</v>
       </c>
     </row>
     <row r="171" spans="1:20">
       <c r="A171" t="s">
-        <v>694</v>
+        <v>691</v>
       </c>
       <c r="B171" t="s">
-        <v>695</v>
+        <v>692</v>
       </c>
       <c r="C171" t="s">
         <v>20</v>
@@ -13360,10 +13336,10 @@
         <v>21</v>
       </c>
       <c r="E171" t="s">
-        <v>439</v>
+        <v>38</v>
       </c>
       <c r="F171" t="s">
-        <v>696</v>
+        <v>693</v>
       </c>
       <c r="G171" t="s">
         <v>23</v>
@@ -13410,10 +13386,10 @@
     </row>
     <row r="172" spans="1:20">
       <c r="A172" t="s">
-        <v>697</v>
+        <v>694</v>
       </c>
       <c r="B172" t="s">
-        <v>698</v>
+        <v>695</v>
       </c>
       <c r="C172" t="s">
         <v>20</v>
@@ -13422,10 +13398,10 @@
         <v>21</v>
       </c>
       <c r="E172" t="s">
-        <v>64</v>
+        <v>439</v>
       </c>
       <c r="F172" t="s">
-        <v>699</v>
+        <v>696</v>
       </c>
       <c r="G172" t="s">
         <v>23</v>
@@ -13472,22 +13448,22 @@
     </row>
     <row r="173" spans="1:20">
       <c r="A173" t="s">
-        <v>700</v>
+        <v>697</v>
       </c>
       <c r="B173" t="s">
-        <v>701</v>
+        <v>698</v>
       </c>
       <c r="C173" t="s">
         <v>20</v>
       </c>
       <c r="D173" t="s">
-        <v>154</v>
+        <v>21</v>
       </c>
       <c r="E173" t="s">
-        <v>421</v>
+        <v>64</v>
       </c>
       <c r="F173" t="s">
-        <v>702</v>
+        <v>699</v>
       </c>
       <c r="G173" t="s">
         <v>23</v>
@@ -13534,22 +13510,22 @@
     </row>
     <row r="174" spans="1:20">
       <c r="A174" t="s">
-        <v>703</v>
+        <v>700</v>
       </c>
       <c r="B174" t="s">
-        <v>704</v>
+        <v>701</v>
       </c>
       <c r="C174" t="s">
         <v>20</v>
       </c>
       <c r="D174" t="s">
-        <v>21</v>
+        <v>154</v>
       </c>
       <c r="E174" t="s">
-        <v>402</v>
+        <v>421</v>
       </c>
       <c r="F174" t="s">
-        <v>705</v>
+        <v>702</v>
       </c>
       <c r="G174" t="s">
         <v>23</v>
@@ -13596,22 +13572,22 @@
     </row>
     <row r="175" spans="1:20">
       <c r="A175" t="s">
-        <v>706</v>
+        <v>703</v>
       </c>
       <c r="B175" t="s">
-        <v>707</v>
+        <v>704</v>
       </c>
       <c r="C175" t="s">
         <v>20</v>
       </c>
       <c r="D175" t="s">
-        <v>42</v>
+        <v>21</v>
       </c>
       <c r="E175" t="s">
-        <v>708</v>
+        <v>402</v>
       </c>
       <c r="F175" t="s">
-        <v>709</v>
+        <v>705</v>
       </c>
       <c r="G175" t="s">
         <v>23</v>
@@ -13658,22 +13634,22 @@
     </row>
     <row r="176" spans="1:20">
       <c r="A176" t="s">
-        <v>710</v>
+        <v>706</v>
       </c>
       <c r="B176" t="s">
-        <v>711</v>
+        <v>707</v>
       </c>
       <c r="C176" t="s">
         <v>20</v>
       </c>
       <c r="D176" t="s">
-        <v>21</v>
+        <v>42</v>
       </c>
       <c r="E176" t="s">
-        <v>22</v>
+        <v>708</v>
       </c>
       <c r="F176" t="s">
-        <v>712</v>
+        <v>709</v>
       </c>
       <c r="G176" t="s">
         <v>23</v>
@@ -13720,22 +13696,22 @@
     </row>
     <row r="177" spans="1:20">
       <c r="A177" t="s">
-        <v>715</v>
+        <v>710</v>
       </c>
       <c r="B177" t="s">
-        <v>716</v>
+        <v>711</v>
       </c>
       <c r="C177" t="s">
         <v>20</v>
       </c>
       <c r="D177" t="s">
-        <v>375</v>
+        <v>21</v>
       </c>
       <c r="E177" t="s">
-        <v>609</v>
+        <v>22</v>
       </c>
       <c r="F177" t="s">
-        <v>717</v>
+        <v>712</v>
       </c>
       <c r="G177" t="s">
         <v>23</v>
@@ -13782,22 +13758,22 @@
     </row>
     <row r="178" spans="1:20">
       <c r="A178" t="s">
-        <v>718</v>
+        <v>715</v>
       </c>
       <c r="B178" t="s">
-        <v>185</v>
+        <v>716</v>
       </c>
       <c r="C178" t="s">
         <v>20</v>
       </c>
       <c r="D178" t="s">
-        <v>42</v>
+        <v>375</v>
       </c>
       <c r="E178" t="s">
-        <v>148</v>
+        <v>609</v>
       </c>
       <c r="F178" t="s">
-        <v>719</v>
+        <v>717</v>
       </c>
       <c r="G178" t="s">
         <v>23</v>
@@ -13844,22 +13820,22 @@
     </row>
     <row r="179" spans="1:20">
       <c r="A179" t="s">
-        <v>720</v>
+        <v>718</v>
       </c>
       <c r="B179" t="s">
-        <v>721</v>
+        <v>185</v>
       </c>
       <c r="C179" t="s">
         <v>20</v>
       </c>
       <c r="D179" t="s">
-        <v>21</v>
+        <v>42</v>
       </c>
       <c r="E179" t="s">
-        <v>22</v>
+        <v>148</v>
       </c>
       <c r="F179" t="s">
-        <v>722</v>
+        <v>719</v>
       </c>
       <c r="G179" t="s">
         <v>23</v>
@@ -13877,7 +13853,7 @@
         <v>23</v>
       </c>
       <c r="L179" t="s">
-        <v>723</v>
+        <v>23</v>
       </c>
       <c r="M179" t="s">
         <v>23</v>
@@ -13906,10 +13882,10 @@
     </row>
     <row r="180" spans="1:20">
       <c r="A180" t="s">
-        <v>724</v>
+        <v>720</v>
       </c>
       <c r="B180" t="s">
-        <v>725</v>
+        <v>721</v>
       </c>
       <c r="C180" t="s">
         <v>20</v>
@@ -13918,10 +13894,10 @@
         <v>21</v>
       </c>
       <c r="E180" t="s">
-        <v>190</v>
+        <v>22</v>
       </c>
       <c r="F180" t="s">
-        <v>726</v>
+        <v>722</v>
       </c>
       <c r="G180" t="s">
         <v>23</v>
@@ -13939,7 +13915,7 @@
         <v>23</v>
       </c>
       <c r="L180" t="s">
-        <v>727</v>
+        <v>723</v>
       </c>
       <c r="M180" t="s">
         <v>23</v>
@@ -13968,10 +13944,10 @@
     </row>
     <row r="181" spans="1:20">
       <c r="A181" t="s">
-        <v>728</v>
+        <v>724</v>
       </c>
       <c r="B181" t="s">
-        <v>729</v>
+        <v>725</v>
       </c>
       <c r="C181" t="s">
         <v>20</v>
@@ -13980,10 +13956,10 @@
         <v>21</v>
       </c>
       <c r="E181" t="s">
-        <v>22</v>
+        <v>190</v>
       </c>
       <c r="F181" t="s">
-        <v>730</v>
+        <v>726</v>
       </c>
       <c r="G181" t="s">
         <v>23</v>
@@ -14001,7 +13977,7 @@
         <v>23</v>
       </c>
       <c r="L181" t="s">
-        <v>731</v>
+        <v>727</v>
       </c>
       <c r="M181" t="s">
         <v>23</v>
@@ -14030,22 +14006,22 @@
     </row>
     <row r="182" spans="1:20">
       <c r="A182" t="s">
-        <v>732</v>
+        <v>728</v>
       </c>
       <c r="B182" t="s">
-        <v>733</v>
+        <v>729</v>
       </c>
       <c r="C182" t="s">
         <v>20</v>
       </c>
       <c r="D182" t="s">
-        <v>485</v>
+        <v>21</v>
       </c>
       <c r="E182" t="s">
-        <v>486</v>
+        <v>22</v>
       </c>
       <c r="F182" t="s">
-        <v>734</v>
+        <v>730</v>
       </c>
       <c r="G182" t="s">
         <v>23</v>
@@ -14063,7 +14039,7 @@
         <v>23</v>
       </c>
       <c r="L182" t="s">
-        <v>735</v>
+        <v>731</v>
       </c>
       <c r="M182" t="s">
         <v>23</v>
@@ -14092,22 +14068,22 @@
     </row>
     <row r="183" spans="1:20">
       <c r="A183" t="s">
-        <v>736</v>
+        <v>732</v>
       </c>
       <c r="B183" t="s">
-        <v>737</v>
+        <v>733</v>
       </c>
       <c r="C183" t="s">
         <v>20</v>
       </c>
       <c r="D183" t="s">
-        <v>21</v>
+        <v>485</v>
       </c>
       <c r="E183" t="s">
-        <v>38</v>
+        <v>486</v>
       </c>
       <c r="F183" t="s">
-        <v>738</v>
+        <v>734</v>
       </c>
       <c r="G183" t="s">
         <v>23</v>
@@ -14125,7 +14101,7 @@
         <v>23</v>
       </c>
       <c r="L183" t="s">
-        <v>739</v>
+        <v>735</v>
       </c>
       <c r="M183" t="s">
         <v>23</v>
@@ -14154,10 +14130,10 @@
     </row>
     <row r="184" spans="1:20">
       <c r="A184" t="s">
-        <v>740</v>
+        <v>736</v>
       </c>
       <c r="B184" t="s">
-        <v>741</v>
+        <v>737</v>
       </c>
       <c r="C184" t="s">
         <v>20</v>
@@ -14166,10 +14142,10 @@
         <v>21</v>
       </c>
       <c r="E184" t="s">
-        <v>22</v>
+        <v>38</v>
       </c>
       <c r="F184" t="s">
-        <v>742</v>
+        <v>738</v>
       </c>
       <c r="G184" t="s">
         <v>23</v>
@@ -14187,7 +14163,7 @@
         <v>23</v>
       </c>
       <c r="L184" t="s">
-        <v>23</v>
+        <v>739</v>
       </c>
       <c r="M184" t="s">
         <v>23</v>
@@ -14216,10 +14192,10 @@
     </row>
     <row r="185" spans="1:20">
       <c r="A185" t="s">
-        <v>743</v>
+        <v>740</v>
       </c>
       <c r="B185" t="s">
-        <v>744</v>
+        <v>741</v>
       </c>
       <c r="C185" t="s">
         <v>20</v>
@@ -14228,10 +14204,10 @@
         <v>21</v>
       </c>
       <c r="E185" t="s">
-        <v>745</v>
+        <v>22</v>
       </c>
       <c r="F185" t="s">
-        <v>746</v>
+        <v>742</v>
       </c>
       <c r="G185" t="s">
         <v>23</v>
@@ -14249,7 +14225,7 @@
         <v>23</v>
       </c>
       <c r="L185" t="s">
-        <v>747</v>
+        <v>23</v>
       </c>
       <c r="M185" t="s">
         <v>23</v>
@@ -14278,10 +14254,10 @@
     </row>
     <row r="186" spans="1:20">
       <c r="A186" t="s">
-        <v>748</v>
+        <v>743</v>
       </c>
       <c r="B186" t="s">
-        <v>749</v>
+        <v>744</v>
       </c>
       <c r="C186" t="s">
         <v>20</v>
@@ -14290,10 +14266,10 @@
         <v>21</v>
       </c>
       <c r="E186" t="s">
-        <v>22</v>
+        <v>745</v>
       </c>
       <c r="F186" t="s">
-        <v>750</v>
+        <v>746</v>
       </c>
       <c r="G186" t="s">
         <v>23</v>
@@ -14311,7 +14287,7 @@
         <v>23</v>
       </c>
       <c r="L186" t="s">
-        <v>751</v>
+        <v>747</v>
       </c>
       <c r="M186" t="s">
         <v>23</v>
@@ -14340,10 +14316,10 @@
     </row>
     <row r="187" spans="1:20">
       <c r="A187" t="s">
-        <v>752</v>
+        <v>748</v>
       </c>
       <c r="B187" t="s">
-        <v>753</v>
+        <v>749</v>
       </c>
       <c r="C187" t="s">
         <v>20</v>
@@ -14352,10 +14328,10 @@
         <v>21</v>
       </c>
       <c r="E187" t="s">
-        <v>38</v>
+        <v>22</v>
       </c>
       <c r="F187" t="s">
-        <v>754</v>
+        <v>750</v>
       </c>
       <c r="G187" t="s">
         <v>23</v>
@@ -14373,7 +14349,7 @@
         <v>23</v>
       </c>
       <c r="L187" t="s">
-        <v>755</v>
+        <v>751</v>
       </c>
       <c r="M187" t="s">
         <v>23</v>
@@ -14402,10 +14378,10 @@
     </row>
     <row r="188" spans="1:20">
       <c r="A188" t="s">
-        <v>756</v>
+        <v>752</v>
       </c>
       <c r="B188" t="s">
-        <v>757</v>
+        <v>753</v>
       </c>
       <c r="C188" t="s">
         <v>20</v>
@@ -14417,7 +14393,7 @@
         <v>38</v>
       </c>
       <c r="F188" t="s">
-        <v>758</v>
+        <v>754</v>
       </c>
       <c r="G188" t="s">
         <v>23</v>
@@ -14435,7 +14411,7 @@
         <v>23</v>
       </c>
       <c r="L188" t="s">
-        <v>759</v>
+        <v>755</v>
       </c>
       <c r="M188" t="s">
         <v>23</v>
@@ -14464,22 +14440,22 @@
     </row>
     <row r="189" spans="1:20">
       <c r="A189" t="s">
-        <v>760</v>
+        <v>756</v>
       </c>
       <c r="B189" t="s">
-        <v>761</v>
+        <v>757</v>
       </c>
       <c r="C189" t="s">
         <v>20</v>
       </c>
       <c r="D189" t="s">
-        <v>375</v>
+        <v>21</v>
       </c>
       <c r="E189" t="s">
-        <v>609</v>
+        <v>38</v>
       </c>
       <c r="F189" t="s">
-        <v>762</v>
+        <v>758</v>
       </c>
       <c r="G189" t="s">
         <v>23</v>
@@ -14497,7 +14473,7 @@
         <v>23</v>
       </c>
       <c r="L189" t="s">
-        <v>23</v>
+        <v>759</v>
       </c>
       <c r="M189" t="s">
         <v>23</v>
@@ -14526,22 +14502,22 @@
     </row>
     <row r="190" spans="1:20">
       <c r="A190" t="s">
-        <v>763</v>
+        <v>760</v>
       </c>
       <c r="B190" t="s">
-        <v>764</v>
+        <v>761</v>
       </c>
       <c r="C190" t="s">
         <v>20</v>
       </c>
       <c r="D190" t="s">
-        <v>21</v>
+        <v>375</v>
       </c>
       <c r="E190" t="s">
-        <v>22</v>
+        <v>609</v>
       </c>
       <c r="F190" t="s">
-        <v>765</v>
+        <v>762</v>
       </c>
       <c r="G190" t="s">
         <v>23</v>
@@ -14559,7 +14535,7 @@
         <v>23</v>
       </c>
       <c r="L190" t="s">
-        <v>766</v>
+        <v>23</v>
       </c>
       <c r="M190" t="s">
         <v>23</v>
@@ -14588,10 +14564,10 @@
     </row>
     <row r="191" spans="1:20">
       <c r="A191" t="s">
-        <v>767</v>
+        <v>763</v>
       </c>
       <c r="B191" t="s">
-        <v>768</v>
+        <v>764</v>
       </c>
       <c r="C191" t="s">
         <v>20</v>
@@ -14603,7 +14579,7 @@
         <v>22</v>
       </c>
       <c r="F191" t="s">
-        <v>769</v>
+        <v>765</v>
       </c>
       <c r="G191" t="s">
         <v>23</v>
@@ -14621,7 +14597,7 @@
         <v>23</v>
       </c>
       <c r="L191" t="s">
-        <v>770</v>
+        <v>766</v>
       </c>
       <c r="M191" t="s">
         <v>23</v>
@@ -14650,10 +14626,10 @@
     </row>
     <row r="192" spans="1:20">
       <c r="A192" t="s">
-        <v>771</v>
+        <v>767</v>
       </c>
       <c r="B192" t="s">
-        <v>772</v>
+        <v>768</v>
       </c>
       <c r="C192" t="s">
         <v>20</v>
@@ -14665,7 +14641,7 @@
         <v>22</v>
       </c>
       <c r="F192" t="s">
-        <v>773</v>
+        <v>769</v>
       </c>
       <c r="G192" t="s">
         <v>23</v>
@@ -14683,7 +14659,7 @@
         <v>23</v>
       </c>
       <c r="L192" t="s">
-        <v>774</v>
+        <v>770</v>
       </c>
       <c r="M192" t="s">
         <v>23</v>
@@ -14712,10 +14688,10 @@
     </row>
     <row r="193" spans="1:20">
       <c r="A193" t="s">
-        <v>775</v>
+        <v>771</v>
       </c>
       <c r="B193" t="s">
-        <v>776</v>
+        <v>772</v>
       </c>
       <c r="C193" t="s">
         <v>20</v>
@@ -14724,10 +14700,10 @@
         <v>21</v>
       </c>
       <c r="E193" t="s">
-        <v>402</v>
+        <v>22</v>
       </c>
       <c r="F193" t="s">
-        <v>777</v>
+        <v>773</v>
       </c>
       <c r="G193" t="s">
         <v>23</v>
@@ -14745,7 +14721,7 @@
         <v>23</v>
       </c>
       <c r="L193" t="s">
-        <v>778</v>
+        <v>774</v>
       </c>
       <c r="M193" t="s">
         <v>23</v>
@@ -14774,10 +14750,10 @@
     </row>
     <row r="194" spans="1:20">
       <c r="A194" t="s">
-        <v>779</v>
+        <v>775</v>
       </c>
       <c r="B194" t="s">
-        <v>780</v>
+        <v>776</v>
       </c>
       <c r="C194" t="s">
         <v>20</v>
@@ -14786,10 +14762,10 @@
         <v>21</v>
       </c>
       <c r="E194" t="s">
-        <v>434</v>
+        <v>402</v>
       </c>
       <c r="F194" t="s">
-        <v>781</v>
+        <v>777</v>
       </c>
       <c r="G194" t="s">
         <v>23</v>
@@ -14807,7 +14783,7 @@
         <v>23</v>
       </c>
       <c r="L194" t="s">
-        <v>782</v>
+        <v>778</v>
       </c>
       <c r="M194" t="s">
         <v>23</v>
@@ -14825,21 +14801,21 @@
         <v>23</v>
       </c>
       <c r="R194" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="S194">
         <v>0</v>
       </c>
       <c r="T194" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
     </row>
     <row r="195" spans="1:20">
       <c r="A195" t="s">
-        <v>783</v>
+        <v>779</v>
       </c>
       <c r="B195" t="s">
-        <v>784</v>
+        <v>780</v>
       </c>
       <c r="C195" t="s">
         <v>20</v>
@@ -14848,10 +14824,10 @@
         <v>21</v>
       </c>
       <c r="E195" t="s">
-        <v>402</v>
+        <v>434</v>
       </c>
       <c r="F195" t="s">
-        <v>785</v>
+        <v>781</v>
       </c>
       <c r="G195" t="s">
         <v>23</v>
@@ -14869,7 +14845,7 @@
         <v>23</v>
       </c>
       <c r="L195" t="s">
-        <v>786</v>
+        <v>782</v>
       </c>
       <c r="M195" t="s">
         <v>23</v>
@@ -14887,33 +14863,33 @@
         <v>23</v>
       </c>
       <c r="R195" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="S195">
         <v>0</v>
       </c>
       <c r="T195" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
     </row>
     <row r="196" spans="1:20">
       <c r="A196" t="s">
-        <v>787</v>
+        <v>783</v>
       </c>
       <c r="B196" t="s">
-        <v>788</v>
+        <v>784</v>
       </c>
       <c r="C196" t="s">
         <v>20</v>
       </c>
       <c r="D196" t="s">
-        <v>713</v>
+        <v>21</v>
       </c>
       <c r="E196" t="s">
-        <v>714</v>
+        <v>402</v>
       </c>
       <c r="F196" t="s">
-        <v>789</v>
+        <v>785</v>
       </c>
       <c r="G196" t="s">
         <v>23</v>
@@ -14931,7 +14907,7 @@
         <v>23</v>
       </c>
       <c r="L196" t="s">
-        <v>790</v>
+        <v>786</v>
       </c>
       <c r="M196" t="s">
         <v>23</v>
@@ -14960,22 +14936,22 @@
     </row>
     <row r="197" spans="1:20">
       <c r="A197" t="s">
-        <v>791</v>
+        <v>787</v>
       </c>
       <c r="B197" t="s">
-        <v>792</v>
+        <v>788</v>
       </c>
       <c r="C197" t="s">
         <v>20</v>
       </c>
       <c r="D197" t="s">
-        <v>21</v>
+        <v>713</v>
       </c>
       <c r="E197" t="s">
-        <v>38</v>
+        <v>714</v>
       </c>
       <c r="F197" t="s">
-        <v>793</v>
+        <v>789</v>
       </c>
       <c r="G197" t="s">
         <v>23</v>
@@ -14993,7 +14969,7 @@
         <v>23</v>
       </c>
       <c r="L197" t="s">
-        <v>794</v>
+        <v>790</v>
       </c>
       <c r="M197" t="s">
         <v>23</v>
@@ -15011,21 +14987,21 @@
         <v>23</v>
       </c>
       <c r="R197" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="S197">
         <v>0</v>
       </c>
       <c r="T197" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
     </row>
     <row r="198" spans="1:20">
       <c r="A198" t="s">
-        <v>795</v>
+        <v>791</v>
       </c>
       <c r="B198" t="s">
-        <v>796</v>
+        <v>792</v>
       </c>
       <c r="C198" t="s">
         <v>20</v>
@@ -15034,10 +15010,10 @@
         <v>21</v>
       </c>
       <c r="E198" t="s">
-        <v>22</v>
+        <v>38</v>
       </c>
       <c r="F198" t="s">
-        <v>797</v>
+        <v>793</v>
       </c>
       <c r="G198" t="s">
         <v>23</v>
@@ -15046,7 +15022,7 @@
         <v>23</v>
       </c>
       <c r="I198" t="s">
-        <v>798</v>
+        <v>23</v>
       </c>
       <c r="J198" t="s">
         <v>23</v>
@@ -15055,7 +15031,7 @@
         <v>23</v>
       </c>
       <c r="L198" t="s">
-        <v>799</v>
+        <v>794</v>
       </c>
       <c r="M198" t="s">
         <v>23</v>
@@ -15073,21 +15049,21 @@
         <v>23</v>
       </c>
       <c r="R198" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="S198">
         <v>0</v>
       </c>
       <c r="T198" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
     </row>
     <row r="199" spans="1:20">
       <c r="A199" t="s">
-        <v>800</v>
+        <v>795</v>
       </c>
       <c r="B199" t="s">
-        <v>801</v>
+        <v>796</v>
       </c>
       <c r="C199" t="s">
         <v>20</v>
@@ -15096,51 +15072,113 @@
         <v>21</v>
       </c>
       <c r="E199" t="s">
+        <v>22</v>
+      </c>
+      <c r="F199" t="s">
+        <v>797</v>
+      </c>
+      <c r="G199" t="s">
+        <v>23</v>
+      </c>
+      <c r="H199" t="s">
+        <v>23</v>
+      </c>
+      <c r="I199" t="s">
+        <v>798</v>
+      </c>
+      <c r="J199" t="s">
+        <v>23</v>
+      </c>
+      <c r="K199" t="s">
+        <v>23</v>
+      </c>
+      <c r="L199" t="s">
+        <v>799</v>
+      </c>
+      <c r="M199" t="s">
+        <v>23</v>
+      </c>
+      <c r="N199" t="s">
+        <v>23</v>
+      </c>
+      <c r="O199" t="s">
+        <v>23</v>
+      </c>
+      <c r="P199" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q199" t="s">
+        <v>23</v>
+      </c>
+      <c r="R199" t="s">
+        <v>23</v>
+      </c>
+      <c r="S199">
+        <v>0</v>
+      </c>
+      <c r="T199" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="200" spans="1:20">
+      <c r="A200" t="s">
+        <v>800</v>
+      </c>
+      <c r="B200" t="s">
+        <v>801</v>
+      </c>
+      <c r="C200" t="s">
+        <v>20</v>
+      </c>
+      <c r="D200" t="s">
+        <v>21</v>
+      </c>
+      <c r="E200" t="s">
         <v>802</v>
       </c>
-      <c r="F199" t="s">
+      <c r="F200" t="s">
         <v>803</v>
       </c>
-      <c r="G199" t="s">
-        <v>23</v>
-      </c>
-      <c r="H199" t="s">
-        <v>23</v>
-      </c>
-      <c r="I199" t="s">
-        <v>23</v>
-      </c>
-      <c r="J199" t="s">
-        <v>23</v>
-      </c>
-      <c r="K199" t="s">
-        <v>23</v>
-      </c>
-      <c r="L199" t="s">
+      <c r="G200" t="s">
+        <v>23</v>
+      </c>
+      <c r="H200" t="s">
+        <v>23</v>
+      </c>
+      <c r="I200" t="s">
+        <v>23</v>
+      </c>
+      <c r="J200" t="s">
+        <v>23</v>
+      </c>
+      <c r="K200" t="s">
+        <v>23</v>
+      </c>
+      <c r="L200" t="s">
         <v>804</v>
       </c>
-      <c r="M199" t="s">
-        <v>23</v>
-      </c>
-      <c r="N199" t="s">
-        <v>23</v>
-      </c>
-      <c r="O199" t="s">
-        <v>23</v>
-      </c>
-      <c r="P199" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q199" t="s">
-        <v>23</v>
-      </c>
-      <c r="R199" t="s">
+      <c r="M200" t="s">
+        <v>23</v>
+      </c>
+      <c r="N200" t="s">
+        <v>23</v>
+      </c>
+      <c r="O200" t="s">
+        <v>23</v>
+      </c>
+      <c r="P200" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q200" t="s">
+        <v>23</v>
+      </c>
+      <c r="R200" t="s">
         <v>612</v>
       </c>
-      <c r="S199">
-        <v>0</v>
-      </c>
-      <c r="T199" t="s">
+      <c r="S200">
+        <v>0</v>
+      </c>
+      <c r="T200" t="s">
         <v>613</v>
       </c>
     </row>

--- a/LISTA_CLIENTI.xlsx
+++ b/LISTA_CLIENTI.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3789" uniqueCount="810">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3795" uniqueCount="813">
   <si>
     <t>denumire</t>
   </si>
@@ -2444,6 +2444,15 @@
   </si>
   <si>
     <t>J2026018147005</t>
+  </si>
+  <si>
+    <t>UNATRANSCAR SRL</t>
+  </si>
+  <si>
+    <t>STR.AKEXANDRU SAHIA, NR.5</t>
+  </si>
+  <si>
+    <t>J2023001276018</t>
   </si>
 </sst>
 </file>
@@ -2478,11 +2487,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyBorder="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1" applyProtection="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2493,8 +2503,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:T200" totalsRowShown="0">
-  <autoFilter ref="A1:T200"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:T201" totalsRowShown="0">
+  <autoFilter ref="A1:T201"/>
   <tableColumns count="20">
     <tableColumn id="1" name="denumire"/>
     <tableColumn id="2" name="cod_fiscal"/>
@@ -2806,7 +2816,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:T200"/>
+  <dimension ref="A1:T201"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="45.85546875" customWidth="1"/>
@@ -15182,6 +15192,42 @@
         <v>613</v>
       </c>
     </row>
+    <row r="201" spans="1:20">
+      <c r="A201" s="2" t="s">
+        <v>810</v>
+      </c>
+      <c r="B201" s="2">
+        <v>49302206</v>
+      </c>
+      <c r="C201" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D201" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="E201" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="F201" s="2" t="s">
+        <v>811</v>
+      </c>
+      <c r="G201" s="2"/>
+      <c r="H201" s="2"/>
+      <c r="I201" s="2"/>
+      <c r="J201" s="2"/>
+      <c r="K201" s="2"/>
+      <c r="L201" s="2" t="s">
+        <v>812</v>
+      </c>
+      <c r="M201" s="2"/>
+      <c r="N201" s="2"/>
+      <c r="O201" s="2"/>
+      <c r="P201" s="2"/>
+      <c r="Q201" s="2"/>
+      <c r="R201" s="2"/>
+      <c r="S201" s="2"/>
+      <c r="T201" s="2"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
   <pageSetup orientation="portrait" r:id="rId1"/>

--- a/LISTA_CLIENTI.xlsx
+++ b/LISTA_CLIENTI.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3795" uniqueCount="813">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3801" uniqueCount="817">
   <si>
     <t>denumire</t>
   </si>
@@ -2449,10 +2449,22 @@
     <t>UNATRANSCAR SRL</t>
   </si>
   <si>
-    <t>STR.AKEXANDRU SAHIA, NR.5</t>
-  </si>
-  <si>
     <t>J2023001276018</t>
+  </si>
+  <si>
+    <t>LIVIO DARIO SRL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AB </t>
+  </si>
+  <si>
+    <t>STR.ALEXANDRU SAHIA, NR.5</t>
+  </si>
+  <si>
+    <t>STR.IASILOR, NR.87</t>
+  </si>
+  <si>
+    <t>J199800417014</t>
   </si>
 </sst>
 </file>
@@ -2487,12 +2499,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyBorder="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1" applyProtection="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2503,8 +2518,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:T201" totalsRowShown="0">
-  <autoFilter ref="A1:T201"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:T202" totalsRowShown="0">
+  <autoFilter ref="A1:T202"/>
   <tableColumns count="20">
     <tableColumn id="1" name="denumire"/>
     <tableColumn id="2" name="cod_fiscal"/>
@@ -2816,7 +2831,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:T201"/>
+  <dimension ref="A1:T202"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="45.85546875" customWidth="1"/>
@@ -15196,7 +15211,7 @@
       <c r="A201" s="2" t="s">
         <v>810</v>
       </c>
-      <c r="B201" s="2">
+      <c r="B201" s="3">
         <v>49302206</v>
       </c>
       <c r="C201" s="2" t="s">
@@ -15209,7 +15224,7 @@
         <v>209</v>
       </c>
       <c r="F201" s="2" t="s">
-        <v>811</v>
+        <v>814</v>
       </c>
       <c r="G201" s="2"/>
       <c r="H201" s="2"/>
@@ -15217,7 +15232,7 @@
       <c r="J201" s="2"/>
       <c r="K201" s="2"/>
       <c r="L201" s="2" t="s">
-        <v>812</v>
+        <v>811</v>
       </c>
       <c r="M201" s="2"/>
       <c r="N201" s="2"/>
@@ -15228,6 +15243,42 @@
       <c r="S201" s="2"/>
       <c r="T201" s="2"/>
     </row>
+    <row r="202" spans="1:20">
+      <c r="A202" s="2" t="s">
+        <v>812</v>
+      </c>
+      <c r="B202" s="3">
+        <v>11070834</v>
+      </c>
+      <c r="C202" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D202" s="2" t="s">
+        <v>813</v>
+      </c>
+      <c r="E202" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="F202" s="2" t="s">
+        <v>815</v>
+      </c>
+      <c r="G202" s="2"/>
+      <c r="H202" s="2"/>
+      <c r="I202" s="2"/>
+      <c r="J202" s="2"/>
+      <c r="K202" s="2"/>
+      <c r="L202" s="2" t="s">
+        <v>816</v>
+      </c>
+      <c r="M202" s="2"/>
+      <c r="N202" s="2"/>
+      <c r="O202" s="2"/>
+      <c r="P202" s="2"/>
+      <c r="Q202" s="2"/>
+      <c r="R202" s="2"/>
+      <c r="S202" s="2"/>
+      <c r="T202" s="2"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
   <pageSetup orientation="portrait" r:id="rId1"/>

--- a/LISTA_CLIENTI.xlsx
+++ b/LISTA_CLIENTI.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3801" uniqueCount="817">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3807" uniqueCount="820">
   <si>
     <t>denumire</t>
   </si>
@@ -2465,6 +2465,15 @@
   </si>
   <si>
     <t>J199800417014</t>
+  </si>
+  <si>
+    <t>MESTER AUTO AV CENTER SRL</t>
+  </si>
+  <si>
+    <t>STR.MIHAI EMINESCU, NR.17</t>
+  </si>
+  <si>
+    <t>J2022000948012</t>
   </si>
 </sst>
 </file>
@@ -2518,8 +2527,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:T202" totalsRowShown="0">
-  <autoFilter ref="A1:T202"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:T204" totalsRowShown="0">
+  <autoFilter ref="A1:T204"/>
   <tableColumns count="20">
     <tableColumn id="1" name="denumire"/>
     <tableColumn id="2" name="cod_fiscal"/>
@@ -2831,7 +2840,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:T202"/>
+  <dimension ref="A1:T204"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="45.85546875" customWidth="1"/>
@@ -15279,6 +15288,64 @@
       <c r="S202" s="2"/>
       <c r="T202" s="2"/>
     </row>
+    <row r="203" spans="1:20">
+      <c r="A203" s="2" t="s">
+        <v>817</v>
+      </c>
+      <c r="B203" s="2">
+        <v>46490121</v>
+      </c>
+      <c r="C203" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D203" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="E203" s="2" t="s">
+        <v>434</v>
+      </c>
+      <c r="F203" s="2" t="s">
+        <v>818</v>
+      </c>
+      <c r="G203" s="2"/>
+      <c r="H203" s="2"/>
+      <c r="I203" s="2"/>
+      <c r="J203" s="2"/>
+      <c r="K203" s="2"/>
+      <c r="L203" s="2" t="s">
+        <v>819</v>
+      </c>
+      <c r="M203" s="2"/>
+      <c r="N203" s="2"/>
+      <c r="O203" s="2"/>
+      <c r="P203" s="2"/>
+      <c r="Q203" s="2"/>
+      <c r="R203" s="2"/>
+      <c r="S203" s="2"/>
+      <c r="T203" s="2"/>
+    </row>
+    <row r="204" spans="1:20">
+      <c r="A204" s="2"/>
+      <c r="B204" s="2"/>
+      <c r="C204" s="2"/>
+      <c r="D204" s="2"/>
+      <c r="E204" s="2"/>
+      <c r="F204" s="2"/>
+      <c r="G204" s="2"/>
+      <c r="H204" s="2"/>
+      <c r="I204" s="2"/>
+      <c r="J204" s="2"/>
+      <c r="K204" s="2"/>
+      <c r="L204" s="2"/>
+      <c r="M204" s="2"/>
+      <c r="N204" s="2"/>
+      <c r="O204" s="2"/>
+      <c r="P204" s="2"/>
+      <c r="Q204" s="2"/>
+      <c r="R204" s="2"/>
+      <c r="S204" s="2"/>
+      <c r="T204" s="2"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
   <pageSetup orientation="portrait" r:id="rId1"/>

--- a/LISTA_CLIENTI.xlsx
+++ b/LISTA_CLIENTI.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3807" uniqueCount="820">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3813" uniqueCount="823">
   <si>
     <t>denumire</t>
   </si>
@@ -2474,6 +2474,15 @@
   </si>
   <si>
     <t>J2022000948012</t>
+  </si>
+  <si>
+    <t>MCS&amp;SIV UNIVERSAL AUTO SRL</t>
+  </si>
+  <si>
+    <t>LUCIAN BLAGA, NR.5</t>
+  </si>
+  <si>
+    <t>J20/121/2010</t>
   </si>
 </sst>
 </file>
@@ -2527,8 +2536,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:T204" totalsRowShown="0">
-  <autoFilter ref="A1:T204"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:T205" totalsRowShown="0">
+  <autoFilter ref="A1:T205"/>
   <tableColumns count="20">
     <tableColumn id="1" name="denumire"/>
     <tableColumn id="2" name="cod_fiscal"/>
@@ -2840,7 +2849,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:T204"/>
+  <dimension ref="A1:T205"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="45.85546875" customWidth="1"/>
@@ -15325,18 +15334,32 @@
       <c r="T203" s="2"/>
     </row>
     <row r="204" spans="1:20">
-      <c r="A204" s="2"/>
-      <c r="B204" s="2"/>
-      <c r="C204" s="2"/>
-      <c r="D204" s="2"/>
-      <c r="E204" s="2"/>
-      <c r="F204" s="2"/>
+      <c r="A204" s="2" t="s">
+        <v>820</v>
+      </c>
+      <c r="B204" s="2">
+        <v>26512390</v>
+      </c>
+      <c r="C204" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D204" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="E204" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="F204" s="2" t="s">
+        <v>821</v>
+      </c>
       <c r="G204" s="2"/>
       <c r="H204" s="2"/>
       <c r="I204" s="2"/>
       <c r="J204" s="2"/>
       <c r="K204" s="2"/>
-      <c r="L204" s="2"/>
+      <c r="L204" s="2" t="s">
+        <v>822</v>
+      </c>
       <c r="M204" s="2"/>
       <c r="N204" s="2"/>
       <c r="O204" s="2"/>
@@ -15346,6 +15369,28 @@
       <c r="S204" s="2"/>
       <c r="T204" s="2"/>
     </row>
+    <row r="205" spans="1:20">
+      <c r="A205" s="2"/>
+      <c r="B205" s="2"/>
+      <c r="C205" s="2"/>
+      <c r="D205" s="2"/>
+      <c r="E205" s="2"/>
+      <c r="F205" s="2"/>
+      <c r="G205" s="2"/>
+      <c r="H205" s="2"/>
+      <c r="I205" s="2"/>
+      <c r="J205" s="2"/>
+      <c r="K205" s="2"/>
+      <c r="L205" s="2"/>
+      <c r="M205" s="2"/>
+      <c r="N205" s="2"/>
+      <c r="O205" s="2"/>
+      <c r="P205" s="2"/>
+      <c r="Q205" s="2"/>
+      <c r="R205" s="2"/>
+      <c r="S205" s="2"/>
+      <c r="T205" s="2"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
   <pageSetup orientation="portrait" r:id="rId1"/>

--- a/LISTA_CLIENTI.xlsx
+++ b/LISTA_CLIENTI.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3813" uniqueCount="823">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3819" uniqueCount="826">
   <si>
     <t>denumire</t>
   </si>
@@ -2483,6 +2483,15 @@
   </si>
   <si>
     <t>J20/121/2010</t>
+  </si>
+  <si>
+    <t>BUBUC AUTOSERV SRL</t>
+  </si>
+  <si>
+    <t>CALEA CLUJULUI 58</t>
+  </si>
+  <si>
+    <t>J2013000220015</t>
   </si>
 </sst>
 </file>
@@ -15370,18 +15379,34 @@
       <c r="T204" s="2"/>
     </row>
     <row r="205" spans="1:20">
-      <c r="A205" s="2"/>
-      <c r="B205" s="2"/>
-      <c r="C205" s="2"/>
-      <c r="D205" s="2"/>
-      <c r="E205" s="2"/>
-      <c r="F205" s="2"/>
+      <c r="A205" s="2" t="s">
+        <v>823</v>
+      </c>
+      <c r="B205" s="2">
+        <v>31443105</v>
+      </c>
+      <c r="C205" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D205" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="E205" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="F205" s="2" t="s">
+        <v>824</v>
+      </c>
       <c r="G205" s="2"/>
       <c r="H205" s="2"/>
-      <c r="I205" s="2"/>
+      <c r="I205" s="2">
+        <v>760863299</v>
+      </c>
       <c r="J205" s="2"/>
       <c r="K205" s="2"/>
-      <c r="L205" s="2"/>
+      <c r="L205" s="2" t="s">
+        <v>825</v>
+      </c>
       <c r="M205" s="2"/>
       <c r="N205" s="2"/>
       <c r="O205" s="2"/>

--- a/LISTA_CLIENTI.xlsx
+++ b/LISTA_CLIENTI.xlsx
@@ -2476,9 +2476,6 @@
     <t>J2022000948012</t>
   </si>
   <si>
-    <t>MCS&amp;SIV UNIVERSAL AUTO SRL</t>
-  </si>
-  <si>
     <t>LUCIAN BLAGA, NR.5</t>
   </si>
   <si>
@@ -2492,6 +2489,9 @@
   </si>
   <si>
     <t>J2013000220015</t>
+  </si>
+  <si>
+    <t>MCR&amp;SIV UNIVERSAL AUTO SRL</t>
   </si>
 </sst>
 </file>
@@ -15344,7 +15344,7 @@
     </row>
     <row r="204" spans="1:20">
       <c r="A204" s="2" t="s">
-        <v>820</v>
+        <v>825</v>
       </c>
       <c r="B204" s="2">
         <v>26512390</v>
@@ -15359,7 +15359,7 @@
         <v>143</v>
       </c>
       <c r="F204" s="2" t="s">
-        <v>821</v>
+        <v>820</v>
       </c>
       <c r="G204" s="2"/>
       <c r="H204" s="2"/>
@@ -15367,7 +15367,7 @@
       <c r="J204" s="2"/>
       <c r="K204" s="2"/>
       <c r="L204" s="2" t="s">
-        <v>822</v>
+        <v>821</v>
       </c>
       <c r="M204" s="2"/>
       <c r="N204" s="2"/>
@@ -15380,7 +15380,7 @@
     </row>
     <row r="205" spans="1:20">
       <c r="A205" s="2" t="s">
-        <v>823</v>
+        <v>822</v>
       </c>
       <c r="B205" s="2">
         <v>31443105</v>
@@ -15395,7 +15395,7 @@
         <v>88</v>
       </c>
       <c r="F205" s="2" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="G205" s="2"/>
       <c r="H205" s="2"/>
@@ -15405,7 +15405,7 @@
       <c r="J205" s="2"/>
       <c r="K205" s="2"/>
       <c r="L205" s="2" t="s">
-        <v>825</v>
+        <v>824</v>
       </c>
       <c r="M205" s="2"/>
       <c r="N205" s="2"/>

--- a/LISTA_CLIENTI.xlsx
+++ b/LISTA_CLIENTI.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3819" uniqueCount="826">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3825" uniqueCount="830">
   <si>
     <t>denumire</t>
   </si>
@@ -2492,6 +2492,18 @@
   </si>
   <si>
     <t>MCR&amp;SIV UNIVERSAL AUTO SRL</t>
+  </si>
+  <si>
+    <t>ALL SYSTEM INSTALLATION SRL</t>
+  </si>
+  <si>
+    <t>POIANA VADULUI</t>
+  </si>
+  <si>
+    <t>PRINCIPALA 29 C</t>
+  </si>
+  <si>
+    <t>J01/483/2009</t>
   </si>
 </sst>
 </file>
@@ -2545,8 +2557,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:T205" totalsRowShown="0">
-  <autoFilter ref="A1:T205"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:T207" totalsRowShown="0">
+  <autoFilter ref="A1:T207"/>
   <tableColumns count="20">
     <tableColumn id="1" name="denumire"/>
     <tableColumn id="2" name="cod_fiscal"/>
@@ -2858,7 +2870,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:T205"/>
+  <dimension ref="A1:T207"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="45.85546875" customWidth="1"/>
@@ -15416,6 +15428,64 @@
       <c r="S205" s="2"/>
       <c r="T205" s="2"/>
     </row>
+    <row r="206" spans="1:20">
+      <c r="A206" s="2" t="s">
+        <v>826</v>
+      </c>
+      <c r="B206" s="2">
+        <v>17237363</v>
+      </c>
+      <c r="C206" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D206" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="E206" s="2" t="s">
+        <v>827</v>
+      </c>
+      <c r="F206" s="2" t="s">
+        <v>828</v>
+      </c>
+      <c r="G206" s="2"/>
+      <c r="H206" s="2"/>
+      <c r="I206" s="2"/>
+      <c r="J206" s="2"/>
+      <c r="K206" s="2"/>
+      <c r="L206" s="2" t="s">
+        <v>829</v>
+      </c>
+      <c r="M206" s="2"/>
+      <c r="N206" s="2"/>
+      <c r="O206" s="2"/>
+      <c r="P206" s="2"/>
+      <c r="Q206" s="2"/>
+      <c r="R206" s="2"/>
+      <c r="S206" s="2"/>
+      <c r="T206" s="2"/>
+    </row>
+    <row r="207" spans="1:20">
+      <c r="A207" s="2"/>
+      <c r="B207" s="2"/>
+      <c r="C207" s="2"/>
+      <c r="D207" s="2"/>
+      <c r="E207" s="2"/>
+      <c r="F207" s="2"/>
+      <c r="G207" s="2"/>
+      <c r="H207" s="2"/>
+      <c r="I207" s="2"/>
+      <c r="J207" s="2"/>
+      <c r="K207" s="2"/>
+      <c r="L207" s="2"/>
+      <c r="M207" s="2"/>
+      <c r="N207" s="2"/>
+      <c r="O207" s="2"/>
+      <c r="P207" s="2"/>
+      <c r="Q207" s="2"/>
+      <c r="R207" s="2"/>
+      <c r="S207" s="2"/>
+      <c r="T207" s="2"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
   <pageSetup orientation="portrait" r:id="rId1"/>

--- a/LISTA_CLIENTI.xlsx
+++ b/LISTA_CLIENTI.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3825" uniqueCount="830">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3831" uniqueCount="834">
   <si>
     <t>denumire</t>
   </si>
@@ -2504,18 +2504,49 @@
   </si>
   <si>
     <t>J01/483/2009</t>
+  </si>
+  <si>
+    <t>SAFETYAUTOITP SRL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RO </t>
+  </si>
+  <si>
+    <t>Str. Depozitelor 16</t>
+  </si>
+  <si>
+    <t>J20/1859/2022</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="1">
+  <fonts count="4">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF4F4F4F"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF111111"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF4F4F4F"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -2538,7 +2569,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyBorder="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1" applyProtection="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left"/>
@@ -2547,6 +2578,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -15464,19 +15498,33 @@
       <c r="S206" s="2"/>
       <c r="T206" s="2"/>
     </row>
-    <row r="207" spans="1:20">
-      <c r="A207" s="2"/>
-      <c r="B207" s="2"/>
-      <c r="C207" s="2"/>
-      <c r="D207" s="2"/>
-      <c r="E207" s="2"/>
-      <c r="F207" s="2"/>
+    <row r="207" spans="1:20" ht="17.25">
+      <c r="A207" s="4" t="s">
+        <v>830</v>
+      </c>
+      <c r="B207" s="4">
+        <v>47153060</v>
+      </c>
+      <c r="C207" s="2" t="s">
+        <v>831</v>
+      </c>
+      <c r="D207" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="E207" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="F207" s="5" t="s">
+        <v>832</v>
+      </c>
       <c r="G207" s="2"/>
       <c r="H207" s="2"/>
       <c r="I207" s="2"/>
       <c r="J207" s="2"/>
       <c r="K207" s="2"/>
-      <c r="L207" s="2"/>
+      <c r="L207" s="6" t="s">
+        <v>833</v>
+      </c>
       <c r="M207" s="2"/>
       <c r="N207" s="2"/>
       <c r="O207" s="2"/>

--- a/LISTA_CLIENTI.xlsx
+++ b/LISTA_CLIENTI.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3831" uniqueCount="834">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3838" uniqueCount="838">
   <si>
     <t>denumire</t>
   </si>
@@ -2506,9 +2506,6 @@
     <t>J01/483/2009</t>
   </si>
   <si>
-    <t>SAFETYAUTOITP SRL</t>
-  </si>
-  <si>
     <t xml:space="preserve">RO </t>
   </si>
   <si>
@@ -2516,6 +2513,21 @@
   </si>
   <si>
     <t>J20/1859/2022</t>
+  </si>
+  <si>
+    <t>SAFETYAUTOSERV SRL</t>
+  </si>
+  <si>
+    <t>AUTO NIMAR SRL</t>
+  </si>
+  <si>
+    <t>Str.Transilvaniei 157</t>
+  </si>
+  <si>
+    <t>J01/58/2003</t>
+  </si>
+  <si>
+    <t>0 757 798 107</t>
   </si>
 </sst>
 </file>
@@ -2569,7 +2581,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyBorder="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1" applyProtection="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left"/>
@@ -2581,6 +2593,9 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2591,8 +2606,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:T207" totalsRowShown="0">
-  <autoFilter ref="A1:T207"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:T208" totalsRowShown="0">
+  <autoFilter ref="A1:T208"/>
   <tableColumns count="20">
     <tableColumn id="1" name="denumire"/>
     <tableColumn id="2" name="cod_fiscal"/>
@@ -2904,7 +2919,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:T207"/>
+  <dimension ref="A1:T208"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="45.85546875" customWidth="1"/>
@@ -15500,13 +15515,13 @@
     </row>
     <row r="207" spans="1:20" ht="17.25">
       <c r="A207" s="4" t="s">
-        <v>830</v>
+        <v>833</v>
       </c>
       <c r="B207" s="4">
         <v>47153060</v>
       </c>
       <c r="C207" s="2" t="s">
-        <v>831</v>
+        <v>830</v>
       </c>
       <c r="D207" s="2" t="s">
         <v>42</v>
@@ -15515,7 +15530,7 @@
         <v>84</v>
       </c>
       <c r="F207" s="5" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
       <c r="G207" s="2"/>
       <c r="H207" s="2"/>
@@ -15523,7 +15538,7 @@
       <c r="J207" s="2"/>
       <c r="K207" s="2"/>
       <c r="L207" s="6" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="M207" s="2"/>
       <c r="N207" s="2"/>
@@ -15534,6 +15549,44 @@
       <c r="S207" s="2"/>
       <c r="T207" s="2"/>
     </row>
+    <row r="208" spans="1:20">
+      <c r="A208" s="2" t="s">
+        <v>834</v>
+      </c>
+      <c r="B208" s="2">
+        <v>15152880</v>
+      </c>
+      <c r="C208" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D208" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="E208" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="F208" s="2" t="s">
+        <v>835</v>
+      </c>
+      <c r="G208" s="2"/>
+      <c r="H208" s="2"/>
+      <c r="I208" s="7" t="s">
+        <v>837</v>
+      </c>
+      <c r="J208" s="2"/>
+      <c r="K208" s="2"/>
+      <c r="L208" s="2" t="s">
+        <v>836</v>
+      </c>
+      <c r="M208" s="2"/>
+      <c r="N208" s="2"/>
+      <c r="O208" s="2"/>
+      <c r="P208" s="2"/>
+      <c r="Q208" s="2"/>
+      <c r="R208" s="2"/>
+      <c r="S208" s="2"/>
+      <c r="T208" s="2"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
   <pageSetup orientation="portrait" r:id="rId1"/>

--- a/LISTA_CLIENTI.xlsx
+++ b/LISTA_CLIENTI.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3838" uniqueCount="838">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3844" uniqueCount="841">
   <si>
     <t>denumire</t>
   </si>
@@ -2528,6 +2528,15 @@
   </si>
   <si>
     <t>0 757 798 107</t>
+  </si>
+  <si>
+    <t>MONDEXPERT SRL</t>
+  </si>
+  <si>
+    <t>Str.Valea Frumoasei 3AB</t>
+  </si>
+  <si>
+    <t>J2002000035017</t>
   </si>
 </sst>
 </file>
@@ -2606,8 +2615,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:T208" totalsRowShown="0">
-  <autoFilter ref="A1:T208"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:T209" totalsRowShown="0">
+  <autoFilter ref="A1:T209"/>
   <tableColumns count="20">
     <tableColumn id="1" name="denumire"/>
     <tableColumn id="2" name="cod_fiscal"/>
@@ -2919,7 +2928,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:T208"/>
+  <dimension ref="A1:T209"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="45.85546875" customWidth="1"/>
@@ -15587,6 +15596,42 @@
       <c r="S208" s="2"/>
       <c r="T208" s="2"/>
     </row>
+    <row r="209" spans="1:20">
+      <c r="A209" s="2" t="s">
+        <v>838</v>
+      </c>
+      <c r="B209" s="2">
+        <v>14408671</v>
+      </c>
+      <c r="C209" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D209" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="E209" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="F209" s="2" t="s">
+        <v>839</v>
+      </c>
+      <c r="G209" s="2"/>
+      <c r="H209" s="2"/>
+      <c r="I209" s="2"/>
+      <c r="J209" s="2"/>
+      <c r="K209" s="2"/>
+      <c r="L209" s="2" t="s">
+        <v>840</v>
+      </c>
+      <c r="M209" s="2"/>
+      <c r="N209" s="2"/>
+      <c r="O209" s="2"/>
+      <c r="P209" s="2"/>
+      <c r="Q209" s="2"/>
+      <c r="R209" s="2"/>
+      <c r="S209" s="2"/>
+      <c r="T209" s="2"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
